--- a/research/traditional_assets/database/data/singapore/singapore_retail_general.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_retail_general.xlsx
@@ -1659,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1796,22 +1796,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08739319017856016</v>
+        <v>0.08728197175525661</v>
       </c>
       <c r="C2">
-        <v>154.9069762787162</v>
+        <v>153.3978982534226</v>
       </c>
       <c r="D2">
-        <v>148.7169762787162</v>
+        <v>148.7968982534226</v>
       </c>
       <c r="E2">
-        <v>-123.4</v>
+        <v>-121.811</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.589</v>
       </c>
       <c r="G2">
         <v>6.19</v>
@@ -1832,28 +1832,28 @@
         <v>18.05</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07992669999999999</v>
       </c>
       <c r="N2">
-        <v>18.05</v>
+        <v>17.9700733</v>
       </c>
       <c r="O2">
-        <v>3.0685</v>
+        <v>3.054912460999999</v>
       </c>
       <c r="P2">
-        <v>14.9815</v>
+        <v>14.915160839</v>
       </c>
       <c r="Q2">
-        <v>47.1815</v>
+        <v>47.115160839</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08739319017856016</v>
+        <v>0.08774190076288546</v>
       </c>
       <c r="T2">
-        <v>0.9605817593200962</v>
+        <v>0.968635121544699</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>225.8319184953213</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1878,22 +1878,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08728197175525661</v>
+        <v>0.08717075333195305</v>
       </c>
       <c r="C3">
-        <v>153.3978982534226</v>
+        <v>151.8889061760384</v>
       </c>
       <c r="D3">
-        <v>148.7968982534226</v>
+        <v>148.8769061760384</v>
       </c>
       <c r="E3">
-        <v>-121.811</v>
+        <v>-120.222</v>
       </c>
       <c r="F3">
-        <v>1.589</v>
+        <v>3.177999999999999</v>
       </c>
       <c r="G3">
         <v>6.19</v>
@@ -1914,28 +1914,28 @@
         <v>18.05</v>
       </c>
       <c r="M3">
-        <v>0.07992669999999999</v>
+        <v>0.1598534</v>
       </c>
       <c r="N3">
-        <v>17.9700733</v>
+        <v>17.8901466</v>
       </c>
       <c r="O3">
-        <v>3.054912460999999</v>
+        <v>3.041324922</v>
       </c>
       <c r="P3">
-        <v>14.915160839</v>
+        <v>14.848821678</v>
       </c>
       <c r="Q3">
-        <v>47.115160839</v>
+        <v>47.048821678</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08774190076288546</v>
+        <v>0.08809772788974801</v>
       </c>
       <c r="T3">
-        <v>0.968635121544699</v>
+        <v>0.9768528381004162</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>225.8319184953213</v>
+        <v>112.9159592476607</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1960,22 +1960,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08717075333195305</v>
+        <v>0.08705953490864951</v>
       </c>
       <c r="C4">
-        <v>151.8889061760384</v>
+        <v>150.3800001852805</v>
       </c>
       <c r="D4">
-        <v>148.8769061760384</v>
+        <v>148.9570001852805</v>
       </c>
       <c r="E4">
-        <v>-120.222</v>
+        <v>-118.633</v>
       </c>
       <c r="F4">
-        <v>3.177999999999999</v>
+        <v>4.766999999999999</v>
       </c>
       <c r="G4">
         <v>6.19</v>
@@ -1996,28 +1996,28 @@
         <v>18.05</v>
       </c>
       <c r="M4">
-        <v>0.1598534</v>
+        <v>0.2397801</v>
       </c>
       <c r="N4">
-        <v>17.8901466</v>
+        <v>17.8102199</v>
       </c>
       <c r="O4">
-        <v>3.041324922</v>
+        <v>3.027737382999999</v>
       </c>
       <c r="P4">
-        <v>14.848821678</v>
+        <v>14.782482517</v>
       </c>
       <c r="Q4">
-        <v>47.048821678</v>
+        <v>46.982482517</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08809772788974801</v>
+        <v>0.08846089165840156</v>
       </c>
       <c r="T4">
-        <v>0.9768528381004162</v>
+        <v>0.9852399921108904</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.9159592476607</v>
+        <v>75.27730616510711</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2042,22 +2042,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08705953490864951</v>
+        <v>0.08694831648534596</v>
       </c>
       <c r="C5">
-        <v>150.3800001852805</v>
+        <v>148.8711804201644</v>
       </c>
       <c r="D5">
-        <v>148.9570001852805</v>
+        <v>149.0371804201644</v>
       </c>
       <c r="E5">
-        <v>-118.633</v>
+        <v>-117.044</v>
       </c>
       <c r="F5">
-        <v>4.766999999999999</v>
+        <v>6.355999999999999</v>
       </c>
       <c r="G5">
         <v>6.19</v>
@@ -2078,28 +2078,28 @@
         <v>18.05</v>
       </c>
       <c r="M5">
-        <v>0.2397801</v>
+        <v>0.3197068</v>
       </c>
       <c r="N5">
-        <v>17.8102199</v>
+        <v>17.7302932</v>
       </c>
       <c r="O5">
-        <v>3.027737382999999</v>
+        <v>3.014149844</v>
       </c>
       <c r="P5">
-        <v>14.782482517</v>
+        <v>14.716143356</v>
       </c>
       <c r="Q5">
-        <v>46.982482517</v>
+        <v>46.916143356</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08846089165840156</v>
+        <v>0.08883162133890204</v>
       </c>
       <c r="T5">
-        <v>0.9852399921108904</v>
+        <v>0.9938018784965829</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.27730616510711</v>
+        <v>56.45797962383034</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2124,22 +2124,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08694831648534596</v>
+        <v>0.08683709806204241</v>
       </c>
       <c r="C6">
-        <v>148.8711804201644</v>
+        <v>147.3624470200052</v>
       </c>
       <c r="D6">
-        <v>149.0371804201644</v>
+        <v>149.1174470200052</v>
       </c>
       <c r="E6">
-        <v>-117.044</v>
+        <v>-115.455</v>
       </c>
       <c r="F6">
-        <v>6.355999999999999</v>
+        <v>7.944999999999999</v>
       </c>
       <c r="G6">
         <v>6.19</v>
@@ -2160,28 +2160,28 @@
         <v>18.05</v>
       </c>
       <c r="M6">
-        <v>0.3197068</v>
+        <v>0.3996335</v>
       </c>
       <c r="N6">
-        <v>17.7302932</v>
+        <v>17.6503665</v>
       </c>
       <c r="O6">
-        <v>3.014149844</v>
+        <v>3.000562305</v>
       </c>
       <c r="P6">
-        <v>14.716143356</v>
+        <v>14.649804195</v>
       </c>
       <c r="Q6">
-        <v>46.916143356</v>
+        <v>46.849804195</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08883162133890204</v>
+        <v>0.08921015585478148</v>
       </c>
       <c r="T6">
-        <v>0.9938018784965829</v>
+        <v>1.002544015121974</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.45797962383034</v>
+        <v>45.16638369906426</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2206,22 +2206,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08683709806204241</v>
+        <v>0.08672587963873885</v>
       </c>
       <c r="C7">
-        <v>147.3624470200052</v>
+        <v>145.8538001244181</v>
       </c>
       <c r="D7">
-        <v>149.1174470200052</v>
+        <v>149.1978001244181</v>
       </c>
       <c r="E7">
-        <v>-115.455</v>
+        <v>-113.866</v>
       </c>
       <c r="F7">
-        <v>7.944999999999999</v>
+        <v>9.533999999999999</v>
       </c>
       <c r="G7">
         <v>6.19</v>
@@ -2242,28 +2242,28 @@
         <v>18.05</v>
       </c>
       <c r="M7">
-        <v>0.3996335</v>
+        <v>0.4795601999999999</v>
       </c>
       <c r="N7">
-        <v>17.6503665</v>
+        <v>17.5704398</v>
       </c>
       <c r="O7">
-        <v>3.000562305</v>
+        <v>2.986974765999999</v>
       </c>
       <c r="P7">
-        <v>14.649804195</v>
+        <v>14.583465034</v>
       </c>
       <c r="Q7">
-        <v>46.849804195</v>
+        <v>46.783465034</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08921015585478148</v>
+        <v>0.08959674429653069</v>
       </c>
       <c r="T7">
-        <v>1.002544015121974</v>
+        <v>1.011472154654288</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.16638369906426</v>
+        <v>37.63865308255355</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2288,22 +2288,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08672587963873885</v>
+        <v>0.0866146612154353</v>
       </c>
       <c r="C8">
-        <v>145.8538001244181</v>
+        <v>144.3452398733196</v>
       </c>
       <c r="D8">
-        <v>149.1978001244181</v>
+        <v>149.2782398733196</v>
       </c>
       <c r="E8">
-        <v>-113.866</v>
+        <v>-112.277</v>
       </c>
       <c r="F8">
-        <v>9.533999999999999</v>
+        <v>11.123</v>
       </c>
       <c r="G8">
         <v>6.19</v>
@@ -2324,28 +2324,28 @@
         <v>18.05</v>
       </c>
       <c r="M8">
-        <v>0.4795601999999999</v>
+        <v>0.5594868999999999</v>
       </c>
       <c r="N8">
-        <v>17.5704398</v>
+        <v>17.4905131</v>
       </c>
       <c r="O8">
-        <v>2.986974765999999</v>
+        <v>2.973387227</v>
       </c>
       <c r="P8">
-        <v>14.583465034</v>
+        <v>14.517125873</v>
       </c>
       <c r="Q8">
-        <v>46.783465034</v>
+        <v>46.717125873</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08959674429653069</v>
+        <v>0.08999164646820999</v>
       </c>
       <c r="T8">
-        <v>1.011472154654288</v>
+        <v>1.020592297187298</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.63865308255355</v>
+        <v>32.26170264218877</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2370,22 +2370,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08661466121543529</v>
+        <v>0.08650344279213174</v>
       </c>
       <c r="C9">
-        <v>144.3452398733196</v>
+        <v>142.836766406928</v>
       </c>
       <c r="D9">
-        <v>149.2782398733196</v>
+        <v>149.358766406928</v>
       </c>
       <c r="E9">
-        <v>-112.277</v>
+        <v>-110.688</v>
       </c>
       <c r="F9">
-        <v>11.123</v>
+        <v>12.712</v>
       </c>
       <c r="G9">
         <v>6.19</v>
@@ -2406,28 +2406,28 @@
         <v>18.05</v>
       </c>
       <c r="M9">
-        <v>0.5594868999999999</v>
+        <v>0.6394135999999999</v>
       </c>
       <c r="N9">
-        <v>17.4905131</v>
+        <v>17.4105864</v>
       </c>
       <c r="O9">
-        <v>2.973387227</v>
+        <v>2.959799687999999</v>
       </c>
       <c r="P9">
-        <v>14.517125873</v>
+        <v>14.450786712</v>
       </c>
       <c r="Q9">
-        <v>46.717125873</v>
+        <v>46.650786712</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08999164646820999</v>
+        <v>0.09039513346970841</v>
       </c>
       <c r="T9">
-        <v>1.020592297187298</v>
+        <v>1.029910703688416</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.26170264218877</v>
+        <v>28.22898981191517</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2452,22 +2452,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08650344279213174</v>
+        <v>0.08639222436882819</v>
       </c>
       <c r="C10">
-        <v>142.836766406928</v>
+        <v>141.3283798657642</v>
       </c>
       <c r="D10">
-        <v>149.358766406928</v>
+        <v>149.4393798657642</v>
       </c>
       <c r="E10">
-        <v>-110.688</v>
+        <v>-109.099</v>
       </c>
       <c r="F10">
-        <v>12.712</v>
+        <v>14.301</v>
       </c>
       <c r="G10">
         <v>6.19</v>
@@ -2488,28 +2488,28 @@
         <v>18.05</v>
       </c>
       <c r="M10">
-        <v>0.6394135999999999</v>
+        <v>0.7193402999999998</v>
       </c>
       <c r="N10">
-        <v>17.4105864</v>
+        <v>17.3306597</v>
       </c>
       <c r="O10">
-        <v>2.959799687999999</v>
+        <v>2.946212149</v>
       </c>
       <c r="P10">
-        <v>14.450786712</v>
+        <v>14.384447551</v>
       </c>
       <c r="Q10">
-        <v>46.650786712</v>
+        <v>46.584447551</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09039513346970841</v>
+        <v>0.09080748831739362</v>
       </c>
       <c r="T10">
-        <v>1.029910703688416</v>
+        <v>1.039433910332416</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.22898981191517</v>
+        <v>25.09243538836904</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2534,22 +2534,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08639222436882819</v>
+        <v>0.08628100594552465</v>
       </c>
       <c r="C11">
-        <v>141.3283798657642</v>
+        <v>139.8200803906528</v>
       </c>
       <c r="D11">
-        <v>149.4393798657642</v>
+        <v>149.5200803906528</v>
       </c>
       <c r="E11">
-        <v>-109.099</v>
+        <v>-107.51</v>
       </c>
       <c r="F11">
-        <v>14.301</v>
+        <v>15.89</v>
       </c>
       <c r="G11">
         <v>6.19</v>
@@ -2570,28 +2570,28 @@
         <v>18.05</v>
       </c>
       <c r="M11">
-        <v>0.7193402999999998</v>
+        <v>0.7992669999999998</v>
       </c>
       <c r="N11">
-        <v>17.3306597</v>
+        <v>17.250733</v>
       </c>
       <c r="O11">
-        <v>2.946212149</v>
+        <v>2.93262461</v>
       </c>
       <c r="P11">
-        <v>14.384447551</v>
+        <v>14.31810839</v>
       </c>
       <c r="Q11">
-        <v>46.584447551</v>
+        <v>46.51810839</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09080748831739362</v>
+        <v>0.0912290066061385</v>
       </c>
       <c r="T11">
-        <v>1.039433910332416</v>
+        <v>1.049168743790727</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.09243538836904</v>
+        <v>22.58319184953213</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2616,22 +2616,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08628100594552465</v>
+        <v>0.0861697875222211</v>
       </c>
       <c r="C12">
-        <v>139.8200803906528</v>
+        <v>138.3118681227228</v>
       </c>
       <c r="D12">
-        <v>149.5200803906528</v>
+        <v>149.6008681227228</v>
       </c>
       <c r="E12">
-        <v>-107.51</v>
+        <v>-105.921</v>
       </c>
       <c r="F12">
-        <v>15.89</v>
+        <v>17.479</v>
       </c>
       <c r="G12">
         <v>6.19</v>
@@ -2652,28 +2652,28 @@
         <v>18.05</v>
       </c>
       <c r="M12">
-        <v>0.7992669999999999</v>
+        <v>0.8791937</v>
       </c>
       <c r="N12">
-        <v>17.250733</v>
+        <v>17.1708063</v>
       </c>
       <c r="O12">
-        <v>2.93262461</v>
+        <v>2.919037071</v>
       </c>
       <c r="P12">
-        <v>14.31810839</v>
+        <v>14.251769229</v>
       </c>
       <c r="Q12">
-        <v>46.51810839</v>
+        <v>46.451769229</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0912290066061385</v>
+        <v>0.09165999721597876</v>
       </c>
       <c r="T12">
-        <v>1.049168743790727</v>
+        <v>1.059122337551472</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.58319184953213</v>
+        <v>20.53017440866558</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2698,22 +2698,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0861697875222211</v>
+        <v>0.08605856909891753</v>
       </c>
       <c r="C13">
-        <v>138.3118681227228</v>
+        <v>136.8037432034083</v>
       </c>
       <c r="D13">
-        <v>149.6008681227228</v>
+        <v>149.6817432034083</v>
       </c>
       <c r="E13">
-        <v>-105.921</v>
+        <v>-104.332</v>
       </c>
       <c r="F13">
-        <v>17.479</v>
+        <v>19.068</v>
       </c>
       <c r="G13">
         <v>6.19</v>
@@ -2734,28 +2734,28 @@
         <v>18.05</v>
       </c>
       <c r="M13">
-        <v>0.8791937</v>
+        <v>0.9591203999999999</v>
       </c>
       <c r="N13">
-        <v>17.1708063</v>
+        <v>17.0908796</v>
       </c>
       <c r="O13">
-        <v>2.919037071</v>
+        <v>2.905449532</v>
       </c>
       <c r="P13">
-        <v>14.251769229</v>
+        <v>14.185430068</v>
       </c>
       <c r="Q13">
-        <v>46.451769229</v>
+        <v>46.38543006800001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09165999721597876</v>
+        <v>0.09210078306695174</v>
       </c>
       <c r="T13">
-        <v>1.059122337551472</v>
+        <v>1.069302149352234</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.53017440866558</v>
+        <v>18.81932654127678</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2780,22 +2780,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08605856909891753</v>
+        <v>0.08594735067561399</v>
       </c>
       <c r="C14">
-        <v>136.8037432034083</v>
+        <v>135.2957057744492</v>
       </c>
       <c r="D14">
-        <v>149.6817432034083</v>
+        <v>149.7627057744492</v>
       </c>
       <c r="E14">
-        <v>-104.332</v>
+        <v>-102.743</v>
       </c>
       <c r="F14">
-        <v>19.068</v>
+        <v>20.657</v>
       </c>
       <c r="G14">
         <v>6.19</v>
@@ -2816,28 +2816,28 @@
         <v>18.05</v>
       </c>
       <c r="M14">
-        <v>0.9591203999999999</v>
+        <v>1.0390471</v>
       </c>
       <c r="N14">
-        <v>17.0908796</v>
+        <v>17.0109529</v>
       </c>
       <c r="O14">
-        <v>2.905449532</v>
+        <v>2.891861993</v>
       </c>
       <c r="P14">
-        <v>14.185430068</v>
+        <v>14.119090907</v>
       </c>
       <c r="Q14">
-        <v>46.38543006800001</v>
+        <v>46.319090907</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09210078306695174</v>
+        <v>0.09255170192599309</v>
       </c>
       <c r="T14">
-        <v>1.069302149352234</v>
+        <v>1.079715979815083</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.81932654127678</v>
+        <v>17.37168603810164</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2862,22 +2862,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08594735067561399</v>
+        <v>0.08583613225231042</v>
       </c>
       <c r="C15">
-        <v>135.2957057744492</v>
+        <v>133.7877559778927</v>
       </c>
       <c r="D15">
-        <v>149.7627057744492</v>
+        <v>149.8437559778927</v>
       </c>
       <c r="E15">
-        <v>-102.743</v>
+        <v>-101.154</v>
       </c>
       <c r="F15">
-        <v>20.657</v>
+        <v>22.246</v>
       </c>
       <c r="G15">
         <v>6.19</v>
@@ -2898,28 +2898,28 @@
         <v>18.05</v>
       </c>
       <c r="M15">
-        <v>1.0390471</v>
+        <v>1.1189738</v>
       </c>
       <c r="N15">
-        <v>17.0109529</v>
+        <v>16.9310262</v>
       </c>
       <c r="O15">
-        <v>2.891861993</v>
+        <v>2.878274454</v>
       </c>
       <c r="P15">
-        <v>14.119090907</v>
+        <v>14.052751746</v>
       </c>
       <c r="Q15">
-        <v>46.319090907</v>
+        <v>46.252751746</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09255170192599309</v>
+        <v>0.0930131072701284</v>
       </c>
       <c r="T15">
-        <v>1.079715979815083</v>
+        <v>1.090371992381719</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.37168603810164</v>
+        <v>16.13085132109438</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08583613225231042</v>
+        <v>0.08572491382900688</v>
       </c>
       <c r="C16">
-        <v>133.7877559778927</v>
+        <v>132.2798939560932</v>
       </c>
       <c r="D16">
-        <v>149.8437559778927</v>
+        <v>149.9248939560932</v>
       </c>
       <c r="E16">
-        <v>-101.154</v>
+        <v>-99.565</v>
       </c>
       <c r="F16">
-        <v>22.246</v>
+        <v>23.835</v>
       </c>
       <c r="G16">
         <v>6.19</v>
@@ -2980,28 +2980,28 @@
         <v>18.05</v>
       </c>
       <c r="M16">
-        <v>1.1189738</v>
+        <v>1.1989005</v>
       </c>
       <c r="N16">
-        <v>16.9310262</v>
+        <v>16.8510995</v>
       </c>
       <c r="O16">
-        <v>2.878274454</v>
+        <v>2.864686915</v>
       </c>
       <c r="P16">
-        <v>14.052751746</v>
+        <v>13.986412585</v>
       </c>
       <c r="Q16">
-        <v>46.252751746</v>
+        <v>46.186412585</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0930131072701284</v>
+        <v>0.09348536921059633</v>
       </c>
       <c r="T16">
-        <v>1.090371992381719</v>
+        <v>1.101278734655804</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.13085132109438</v>
+        <v>15.05546123302142</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3026,22 +3026,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08572491382900688</v>
+        <v>0.08561369540570332</v>
       </c>
       <c r="C17">
-        <v>132.2798939560932</v>
+        <v>130.7721198517139</v>
       </c>
       <c r="D17">
-        <v>149.9248939560932</v>
+        <v>150.0061198517139</v>
       </c>
       <c r="E17">
-        <v>-99.565</v>
+        <v>-97.976</v>
       </c>
       <c r="F17">
-        <v>23.835</v>
+        <v>25.424</v>
       </c>
       <c r="G17">
         <v>6.19</v>
@@ -3062,28 +3062,28 @@
         <v>18.05</v>
       </c>
       <c r="M17">
-        <v>1.1989005</v>
+        <v>1.2788272</v>
       </c>
       <c r="N17">
-        <v>16.8510995</v>
+        <v>16.7711728</v>
       </c>
       <c r="O17">
-        <v>2.864686915</v>
+        <v>2.851099376</v>
       </c>
       <c r="P17">
-        <v>13.986412585</v>
+        <v>13.920073424</v>
       </c>
       <c r="Q17">
-        <v>46.186412585</v>
+        <v>46.120073424</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09348536921059633</v>
+        <v>0.09396887548298015</v>
       </c>
       <c r="T17">
-        <v>1.101278734655804</v>
+        <v>1.112445161269749</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.05546123302142</v>
+        <v>14.11449490595759</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3108,22 +3108,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08561369540570332</v>
+        <v>0.08550247698239977</v>
       </c>
       <c r="C18">
-        <v>130.7721198517139</v>
+        <v>129.2644338077272</v>
       </c>
       <c r="D18">
-        <v>150.0061198517139</v>
+        <v>150.0874338077272</v>
       </c>
       <c r="E18">
-        <v>-97.976</v>
+        <v>-96.387</v>
       </c>
       <c r="F18">
-        <v>25.424</v>
+        <v>27.013</v>
       </c>
       <c r="G18">
         <v>6.19</v>
@@ -3144,28 +3144,28 @@
         <v>18.05</v>
       </c>
       <c r="M18">
-        <v>1.2788272</v>
+        <v>1.3587539</v>
       </c>
       <c r="N18">
-        <v>16.7711728</v>
+        <v>16.6912461</v>
       </c>
       <c r="O18">
-        <v>2.851099376</v>
+        <v>2.837511837</v>
       </c>
       <c r="P18">
-        <v>13.920073424</v>
+        <v>13.853734263</v>
       </c>
       <c r="Q18">
-        <v>46.120073424</v>
+        <v>46.053734263</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09396887548298015</v>
+        <v>0.09446403250891539</v>
       </c>
       <c r="T18">
-        <v>1.112445161269749</v>
+        <v>1.123880658404512</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.11449490595759</v>
+        <v>13.28423049972479</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3190,22 +3190,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08550247698239977</v>
+        <v>0.0856153585590962</v>
       </c>
       <c r="C19">
-        <v>129.2644338077272</v>
+        <v>127.5929045564947</v>
       </c>
       <c r="D19">
-        <v>150.0874338077272</v>
+        <v>150.0049045564947</v>
       </c>
       <c r="E19">
-        <v>-96.387</v>
+        <v>-94.79799999999999</v>
       </c>
       <c r="F19">
-        <v>27.013</v>
+        <v>28.602</v>
       </c>
       <c r="G19">
         <v>6.19</v>
@@ -3226,45 +3226,45 @@
         <v>18.05</v>
       </c>
       <c r="M19">
-        <v>1.3587539</v>
+        <v>1.4815836</v>
       </c>
       <c r="N19">
-        <v>16.6912461</v>
+        <v>16.5684164</v>
       </c>
       <c r="O19">
-        <v>2.837511837</v>
+        <v>2.816630787999999</v>
       </c>
       <c r="P19">
-        <v>13.853734263</v>
+        <v>13.751785612</v>
       </c>
       <c r="Q19">
-        <v>46.053734263</v>
+        <v>45.951785612</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09446403250891539</v>
+        <v>0.09497126653548318</v>
       </c>
       <c r="T19">
-        <v>1.123880658404512</v>
+        <v>1.135595070103538</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.28423049972479</v>
+        <v>12.18291023199771</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3272,22 +3272,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08561535855909622</v>
+        <v>0.08551659013579267</v>
       </c>
       <c r="C20">
-        <v>127.5929045564946</v>
+        <v>126.0761105231295</v>
       </c>
       <c r="D20">
-        <v>150.0049045564946</v>
+        <v>150.0771105231295</v>
       </c>
       <c r="E20">
-        <v>-94.798</v>
+        <v>-93.209</v>
       </c>
       <c r="F20">
-        <v>28.60199999999999</v>
+        <v>30.191</v>
       </c>
       <c r="G20">
         <v>6.19</v>
@@ -3308,28 +3308,28 @@
         <v>18.05</v>
       </c>
       <c r="M20">
-        <v>1.4815836</v>
+        <v>1.5638938</v>
       </c>
       <c r="N20">
-        <v>16.5684164</v>
+        <v>16.4861062</v>
       </c>
       <c r="O20">
-        <v>2.816630787999999</v>
+        <v>2.802638054</v>
       </c>
       <c r="P20">
-        <v>13.751785612</v>
+        <v>13.683468146</v>
       </c>
       <c r="Q20">
-        <v>45.951785612</v>
+        <v>45.883468146</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09497126653548318</v>
+        <v>0.09549102485900329</v>
       </c>
       <c r="T20">
-        <v>1.135595070103538</v>
+        <v>1.147598726535873</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.18291023199771</v>
+        <v>11.54170443031362</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3354,22 +3354,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08551659013579267</v>
+        <v>0.08541782171248911</v>
       </c>
       <c r="C21">
-        <v>126.0761105231295</v>
+        <v>124.5593860369902</v>
       </c>
       <c r="D21">
-        <v>150.0771105231295</v>
+        <v>150.1493860369902</v>
       </c>
       <c r="E21">
-        <v>-93.209</v>
+        <v>-91.61999999999999</v>
       </c>
       <c r="F21">
-        <v>30.191</v>
+        <v>31.78</v>
       </c>
       <c r="G21">
         <v>6.19</v>
@@ -3390,28 +3390,28 @@
         <v>18.05</v>
       </c>
       <c r="M21">
-        <v>1.5638938</v>
+        <v>1.646204</v>
       </c>
       <c r="N21">
-        <v>16.4861062</v>
+        <v>16.403796</v>
       </c>
       <c r="O21">
-        <v>2.802638054</v>
+        <v>2.78864532</v>
       </c>
       <c r="P21">
-        <v>13.683468146</v>
+        <v>13.61515068</v>
       </c>
       <c r="Q21">
-        <v>45.883468146</v>
+        <v>45.81515068</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09549102485900329</v>
+        <v>0.09602377714061139</v>
       </c>
       <c r="T21">
-        <v>1.147598726535873</v>
+        <v>1.159902474379016</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.54170443031362</v>
+        <v>10.96461920879794</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3436,22 +3436,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08541782171248911</v>
+        <v>0.08531905328918557</v>
       </c>
       <c r="C22">
-        <v>124.5593860369902</v>
+        <v>123.0427311986045</v>
       </c>
       <c r="D22">
-        <v>150.1493860369902</v>
+        <v>150.2217311986045</v>
       </c>
       <c r="E22">
-        <v>-91.61999999999999</v>
+        <v>-90.03099999999999</v>
       </c>
       <c r="F22">
-        <v>31.78</v>
+        <v>33.369</v>
       </c>
       <c r="G22">
         <v>6.19</v>
@@ -3472,28 +3472,28 @@
         <v>18.05</v>
       </c>
       <c r="M22">
-        <v>1.646204</v>
+        <v>1.7285142</v>
       </c>
       <c r="N22">
-        <v>16.403796</v>
+        <v>16.3214858</v>
       </c>
       <c r="O22">
-        <v>2.78864532</v>
+        <v>2.774652586</v>
       </c>
       <c r="P22">
-        <v>13.61515068</v>
+        <v>13.546833214</v>
       </c>
       <c r="Q22">
-        <v>45.81515068</v>
+        <v>45.746833214</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09602377714061139</v>
+        <v>0.09657001682175388</v>
       </c>
       <c r="T22">
-        <v>1.159902474379016</v>
+        <v>1.172517709509328</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.96461920879794</v>
+        <v>10.44249448456946</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3518,22 +3518,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08531905328918557</v>
+        <v>0.08522028486588201</v>
       </c>
       <c r="C23">
-        <v>123.0427311986045</v>
+        <v>121.5261461086945</v>
       </c>
       <c r="D23">
-        <v>150.2217311986045</v>
+        <v>150.2941461086945</v>
       </c>
       <c r="E23">
-        <v>-90.03100000000001</v>
+        <v>-88.44199999999999</v>
       </c>
       <c r="F23">
-        <v>33.36899999999999</v>
+        <v>34.958</v>
       </c>
       <c r="G23">
         <v>6.19</v>
@@ -3554,28 +3554,28 @@
         <v>18.05</v>
       </c>
       <c r="M23">
-        <v>1.7285142</v>
+        <v>1.8108244</v>
       </c>
       <c r="N23">
-        <v>16.3214858</v>
+        <v>16.2391756</v>
       </c>
       <c r="O23">
-        <v>2.774652586</v>
+        <v>2.760659851999999</v>
       </c>
       <c r="P23">
-        <v>13.546833214</v>
+        <v>13.478515748</v>
       </c>
       <c r="Q23">
-        <v>45.746833214</v>
+        <v>45.678515748</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09657001682175388</v>
+        <v>0.09713026264856668</v>
       </c>
       <c r="T23">
-        <v>1.172517709509328</v>
+        <v>1.185456412207083</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.44249448456947</v>
+        <v>9.96783564436176</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3600,22 +3600,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08522028486588201</v>
+        <v>0.08544604644257846</v>
       </c>
       <c r="C24">
-        <v>121.5261461086945</v>
+        <v>119.7717249959018</v>
       </c>
       <c r="D24">
-        <v>150.2941461086945</v>
+        <v>150.1287249959018</v>
       </c>
       <c r="E24">
-        <v>-88.44199999999999</v>
+        <v>-86.85299999999999</v>
       </c>
       <c r="F24">
-        <v>34.958</v>
+        <v>36.547</v>
       </c>
       <c r="G24">
         <v>6.19</v>
@@ -3636,45 +3636,45 @@
         <v>18.05</v>
       </c>
       <c r="M24">
-        <v>1.8108244</v>
+        <v>1.9552645</v>
       </c>
       <c r="N24">
-        <v>16.2391756</v>
+        <v>16.0947355</v>
       </c>
       <c r="O24">
-        <v>2.760659851999999</v>
+        <v>2.736105035</v>
       </c>
       <c r="P24">
-        <v>13.478515748</v>
+        <v>13.358630465</v>
       </c>
       <c r="Q24">
-        <v>45.678515748</v>
+        <v>45.558630465</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09713026264856668</v>
+        <v>0.09770506031503695</v>
       </c>
       <c r="T24">
-        <v>1.185456412207083</v>
+        <v>1.19873118510478</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.17</v>
       </c>
       <c r="W24">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.96783564436176</v>
+        <v>9.231487606919679</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3682,22 +3682,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08544604644257846</v>
+        <v>0.08536138801927491</v>
       </c>
       <c r="C25">
-        <v>119.7717249959018</v>
+        <v>118.2447136347046</v>
       </c>
       <c r="D25">
-        <v>150.1287249959018</v>
+        <v>150.1907136347046</v>
       </c>
       <c r="E25">
-        <v>-86.85299999999999</v>
+        <v>-85.264</v>
       </c>
       <c r="F25">
-        <v>36.547</v>
+        <v>38.136</v>
       </c>
       <c r="G25">
         <v>6.19</v>
@@ -3718,28 +3718,28 @@
         <v>18.05</v>
       </c>
       <c r="M25">
-        <v>1.9552645</v>
+        <v>2.040276</v>
       </c>
       <c r="N25">
-        <v>16.0947355</v>
+        <v>16.009724</v>
       </c>
       <c r="O25">
-        <v>2.736105035</v>
+        <v>2.72165308</v>
       </c>
       <c r="P25">
-        <v>13.358630465</v>
+        <v>13.28807092</v>
       </c>
       <c r="Q25">
-        <v>45.558630465</v>
+        <v>45.48807092</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09770506031503695</v>
+        <v>0.09829498423588803</v>
       </c>
       <c r="T25">
-        <v>1.19873118510478</v>
+        <v>1.212355294131363</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.231487606919679</v>
+        <v>8.846842289964691</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3764,22 +3764,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08536138801927491</v>
+        <v>0.08527672959597135</v>
       </c>
       <c r="C26">
-        <v>118.2447136347046</v>
+        <v>116.717753485274</v>
       </c>
       <c r="D26">
-        <v>150.1907136347046</v>
+        <v>150.252753485274</v>
       </c>
       <c r="E26">
-        <v>-85.264</v>
+        <v>-83.675</v>
       </c>
       <c r="F26">
-        <v>38.136</v>
+        <v>39.72499999999999</v>
       </c>
       <c r="G26">
         <v>6.19</v>
@@ -3800,28 +3800,28 @@
         <v>18.05</v>
       </c>
       <c r="M26">
-        <v>2.040276</v>
+        <v>2.1252875</v>
       </c>
       <c r="N26">
-        <v>16.009724</v>
+        <v>15.9247125</v>
       </c>
       <c r="O26">
-        <v>2.72165308</v>
+        <v>2.707201125</v>
       </c>
       <c r="P26">
-        <v>13.28807092</v>
+        <v>13.217511375</v>
       </c>
       <c r="Q26">
-        <v>45.48807092</v>
+        <v>45.417511375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09829498423588803</v>
+        <v>0.09890063946129514</v>
       </c>
       <c r="T26">
-        <v>1.212355294131363</v>
+        <v>1.226342712731989</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.846842289964691</v>
+        <v>8.492968598366105</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3846,22 +3846,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08527672959597135</v>
+        <v>0.08519207117266779</v>
       </c>
       <c r="C27">
-        <v>116.717753485274</v>
+        <v>115.1908446110991</v>
       </c>
       <c r="D27">
-        <v>150.252753485274</v>
+        <v>150.3148446110991</v>
       </c>
       <c r="E27">
-        <v>-83.675</v>
+        <v>-82.086</v>
       </c>
       <c r="F27">
-        <v>39.72499999999999</v>
+        <v>41.31399999999999</v>
       </c>
       <c r="G27">
         <v>6.19</v>
@@ -3882,28 +3882,28 @@
         <v>18.05</v>
       </c>
       <c r="M27">
-        <v>2.1252875</v>
+        <v>2.210299</v>
       </c>
       <c r="N27">
-        <v>15.9247125</v>
+        <v>15.839701</v>
       </c>
       <c r="O27">
-        <v>2.707201125</v>
+        <v>2.69274917</v>
       </c>
       <c r="P27">
-        <v>13.217511375</v>
+        <v>13.14695183</v>
       </c>
       <c r="Q27">
-        <v>45.417511375</v>
+        <v>45.34695183</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09890063946129514</v>
+        <v>0.09952266374684837</v>
       </c>
       <c r="T27">
-        <v>1.226342712731989</v>
+        <v>1.240708169673173</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.492968598366105</v>
+        <v>8.166315959967408</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3928,22 +3928,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08519207117266779</v>
+        <v>0.08510741274936424</v>
       </c>
       <c r="C28">
-        <v>115.1908446110991</v>
+        <v>113.6639870757736</v>
       </c>
       <c r="D28">
-        <v>150.3148446110991</v>
+        <v>150.3769870757736</v>
       </c>
       <c r="E28">
-        <v>-82.086</v>
+        <v>-80.49699999999999</v>
       </c>
       <c r="F28">
-        <v>41.31399999999999</v>
+        <v>42.903</v>
       </c>
       <c r="G28">
         <v>6.19</v>
@@ -3964,28 +3964,28 @@
         <v>18.05</v>
       </c>
       <c r="M28">
-        <v>2.210299</v>
+        <v>2.2953105</v>
       </c>
       <c r="N28">
-        <v>15.839701</v>
+        <v>15.7546895</v>
       </c>
       <c r="O28">
-        <v>2.69274917</v>
+        <v>2.678297215</v>
       </c>
       <c r="P28">
-        <v>13.14695183</v>
+        <v>13.076392285</v>
       </c>
       <c r="Q28">
-        <v>45.34695183</v>
+        <v>45.276392285</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09952266374684837</v>
+        <v>0.1001617297936497</v>
       </c>
       <c r="T28">
-        <v>1.240708169673173</v>
+        <v>1.255467200777128</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.166315959967408</v>
+        <v>7.863859813301947</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4010,22 +4010,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08510741274936424</v>
+        <v>0.0852086743260607</v>
       </c>
       <c r="C29">
-        <v>113.6639870757736</v>
+        <v>112.0006632960513</v>
       </c>
       <c r="D29">
-        <v>150.3769870757736</v>
+        <v>150.3026632960513</v>
       </c>
       <c r="E29">
-        <v>-80.49699999999999</v>
+        <v>-78.90799999999999</v>
       </c>
       <c r="F29">
-        <v>42.903</v>
+        <v>44.492</v>
       </c>
       <c r="G29">
         <v>6.19</v>
@@ -4046,45 +4046,45 @@
         <v>18.05</v>
       </c>
       <c r="M29">
-        <v>2.2953105</v>
+        <v>2.4159156</v>
       </c>
       <c r="N29">
-        <v>15.7546895</v>
+        <v>15.6340844</v>
       </c>
       <c r="O29">
-        <v>2.678297215</v>
+        <v>2.657794348</v>
       </c>
       <c r="P29">
-        <v>13.076392285</v>
+        <v>12.976290052</v>
       </c>
       <c r="Q29">
-        <v>45.276392285</v>
+        <v>45.176290052</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1001617297936497</v>
+        <v>0.1008185476750843</v>
       </c>
       <c r="T29">
-        <v>1.255467200777128</v>
+        <v>1.270636204967305</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.17</v>
       </c>
       <c r="W29">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.863859813301947</v>
+        <v>7.471287490341135</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4092,22 +4092,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0852086743260607</v>
+        <v>0.08513065590275715</v>
       </c>
       <c r="C30">
-        <v>112.0006632960513</v>
+        <v>110.4689206112566</v>
       </c>
       <c r="D30">
-        <v>150.3026632960513</v>
+        <v>150.3599206112566</v>
       </c>
       <c r="E30">
-        <v>-78.90799999999999</v>
+        <v>-77.31899999999999</v>
       </c>
       <c r="F30">
-        <v>44.492</v>
+        <v>46.081</v>
       </c>
       <c r="G30">
         <v>6.19</v>
@@ -4128,28 +4128,28 @@
         <v>18.05</v>
       </c>
       <c r="M30">
-        <v>2.4159156</v>
+        <v>2.5021983</v>
       </c>
       <c r="N30">
-        <v>15.6340844</v>
+        <v>15.5478017</v>
       </c>
       <c r="O30">
-        <v>2.657794348</v>
+        <v>2.643126289</v>
       </c>
       <c r="P30">
-        <v>12.976290052</v>
+        <v>12.904675411</v>
       </c>
       <c r="Q30">
-        <v>45.176290052</v>
+        <v>45.104675411</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1008185476750843</v>
+        <v>0.101493867468672</v>
       </c>
       <c r="T30">
-        <v>1.270636204967305</v>
+        <v>1.286232505050163</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.471287490341135</v>
+        <v>7.213656887225924</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4174,22 +4174,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08513065590275713</v>
+        <v>0.08505263747945359</v>
       </c>
       <c r="C31">
-        <v>110.4689206112566</v>
+        <v>108.9372215670661</v>
       </c>
       <c r="D31">
-        <v>150.3599206112566</v>
+        <v>150.4172215670661</v>
       </c>
       <c r="E31">
-        <v>-77.319</v>
+        <v>-75.72999999999999</v>
       </c>
       <c r="F31">
-        <v>46.08099999999999</v>
+        <v>47.66999999999999</v>
       </c>
       <c r="G31">
         <v>6.19</v>
@@ -4210,28 +4210,28 @@
         <v>18.05</v>
       </c>
       <c r="M31">
-        <v>2.502198299999999</v>
+        <v>2.588481</v>
       </c>
       <c r="N31">
-        <v>15.5478017</v>
+        <v>15.461519</v>
       </c>
       <c r="O31">
-        <v>2.643126289</v>
+        <v>2.62845823</v>
       </c>
       <c r="P31">
-        <v>12.904675411</v>
+        <v>12.83306077</v>
       </c>
       <c r="Q31">
-        <v>45.104675411</v>
+        <v>45.03306077</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.101493867468672</v>
+        <v>0.1021884821135051</v>
       </c>
       <c r="T31">
-        <v>1.286232505050162</v>
+        <v>1.302274413706816</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.213656887225925</v>
+        <v>6.973201657651726</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4256,22 +4256,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08505263747945359</v>
+        <v>0.08497461905615003</v>
       </c>
       <c r="C32">
-        <v>108.9372215670661</v>
+        <v>107.405566213392</v>
       </c>
       <c r="D32">
-        <v>150.4172215670661</v>
+        <v>150.474566213392</v>
       </c>
       <c r="E32">
-        <v>-75.72999999999999</v>
+        <v>-74.14099999999999</v>
       </c>
       <c r="F32">
-        <v>47.66999999999999</v>
+        <v>49.25899999999999</v>
       </c>
       <c r="G32">
         <v>6.19</v>
@@ -4292,28 +4292,28 @@
         <v>18.05</v>
       </c>
       <c r="M32">
-        <v>2.588481</v>
+        <v>2.6747637</v>
       </c>
       <c r="N32">
-        <v>15.461519</v>
+        <v>15.3752363</v>
       </c>
       <c r="O32">
-        <v>2.62845823</v>
+        <v>2.613790171</v>
       </c>
       <c r="P32">
-        <v>12.83306077</v>
+        <v>12.761446129</v>
       </c>
       <c r="Q32">
-        <v>45.03306077</v>
+        <v>44.961446129</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1021884821135051</v>
+        <v>0.1029032305161595</v>
       </c>
       <c r="T32">
-        <v>1.302274413706816</v>
+        <v>1.318781305223083</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.973201657651726</v>
+        <v>6.748259668695219</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4338,22 +4338,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08497461905615003</v>
+        <v>0.08489660063284647</v>
       </c>
       <c r="C33">
-        <v>107.405566213392</v>
+        <v>105.8739546002228</v>
       </c>
       <c r="D33">
-        <v>150.474566213392</v>
+        <v>150.5319546002227</v>
       </c>
       <c r="E33">
-        <v>-74.14099999999999</v>
+        <v>-72.55199999999999</v>
       </c>
       <c r="F33">
-        <v>49.25899999999999</v>
+        <v>50.84799999999999</v>
       </c>
       <c r="G33">
         <v>6.19</v>
@@ -4374,28 +4374,28 @@
         <v>18.05</v>
       </c>
       <c r="M33">
-        <v>2.6747637</v>
+        <v>2.7610464</v>
       </c>
       <c r="N33">
-        <v>15.3752363</v>
+        <v>15.2889536</v>
       </c>
       <c r="O33">
-        <v>2.613790171</v>
+        <v>2.599122112</v>
       </c>
       <c r="P33">
-        <v>12.761446129</v>
+        <v>12.689831488</v>
       </c>
       <c r="Q33">
-        <v>44.961446129</v>
+        <v>44.889831488</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1029032305161595</v>
+        <v>0.1036390009306566</v>
       </c>
       <c r="T33">
-        <v>1.318781305223083</v>
+        <v>1.335773693548651</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.748259668695219</v>
+        <v>6.537376554048493</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4420,22 +4420,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08489660063284647</v>
+        <v>0.08481858220954294</v>
       </c>
       <c r="C34">
-        <v>105.8739546002228</v>
+        <v>104.342386777623</v>
       </c>
       <c r="D34">
-        <v>150.5319546002227</v>
+        <v>150.589386777623</v>
       </c>
       <c r="E34">
-        <v>-72.55199999999999</v>
+        <v>-70.96299999999999</v>
       </c>
       <c r="F34">
-        <v>50.84799999999999</v>
+        <v>52.437</v>
       </c>
       <c r="G34">
         <v>6.19</v>
@@ -4456,28 +4456,28 @@
         <v>18.05</v>
       </c>
       <c r="M34">
-        <v>2.7610464</v>
+        <v>2.8473291</v>
       </c>
       <c r="N34">
-        <v>15.2889536</v>
+        <v>15.2026709</v>
       </c>
       <c r="O34">
-        <v>2.599122112</v>
+        <v>2.584454053</v>
       </c>
       <c r="P34">
-        <v>12.689831488</v>
+        <v>12.618216847</v>
       </c>
       <c r="Q34">
-        <v>44.889831488</v>
+        <v>44.818216847</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1036390009306566</v>
+        <v>0.1043967346411089</v>
       </c>
       <c r="T34">
-        <v>1.335773693548651</v>
+        <v>1.353273317346625</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.537376554048493</v>
+        <v>6.339274234228842</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4502,22 +4502,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08481858220954294</v>
+        <v>0.08474056378623937</v>
       </c>
       <c r="C35">
-        <v>104.342386777623</v>
+        <v>102.810862795734</v>
       </c>
       <c r="D35">
-        <v>150.589386777623</v>
+        <v>150.646862795734</v>
       </c>
       <c r="E35">
-        <v>-70.96299999999999</v>
+        <v>-69.374</v>
       </c>
       <c r="F35">
-        <v>52.437</v>
+        <v>54.026</v>
       </c>
       <c r="G35">
         <v>6.19</v>
@@ -4538,28 +4538,28 @@
         <v>18.05</v>
       </c>
       <c r="M35">
-        <v>2.8473291</v>
+        <v>2.9336118</v>
       </c>
       <c r="N35">
-        <v>15.2026709</v>
+        <v>15.1163882</v>
       </c>
       <c r="O35">
-        <v>2.584454053</v>
+        <v>2.569785994</v>
       </c>
       <c r="P35">
-        <v>12.618216847</v>
+        <v>12.546602206</v>
       </c>
       <c r="Q35">
-        <v>44.818216847</v>
+        <v>44.746602206</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1043967346411089</v>
+        <v>0.1051774299791506</v>
       </c>
       <c r="T35">
-        <v>1.353273317346625</v>
+        <v>1.37130323277484</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.339274234228842</v>
+        <v>6.152824992045641</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4584,22 +4584,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08474056378623937</v>
+        <v>0.08495304536293583</v>
       </c>
       <c r="C36">
-        <v>102.810862795734</v>
+        <v>101.0654309012358</v>
       </c>
       <c r="D36">
-        <v>150.646862795734</v>
+        <v>150.4904309012358</v>
       </c>
       <c r="E36">
-        <v>-69.374</v>
+        <v>-67.785</v>
       </c>
       <c r="F36">
-        <v>54.026</v>
+        <v>55.61499999999999</v>
       </c>
       <c r="G36">
         <v>6.19</v>
@@ -4620,45 +4620,45 @@
         <v>18.05</v>
       </c>
       <c r="M36">
-        <v>2.9336118</v>
+        <v>3.0755095</v>
       </c>
       <c r="N36">
-        <v>15.1163882</v>
+        <v>14.9744905</v>
       </c>
       <c r="O36">
-        <v>2.569785994</v>
+        <v>2.545663385</v>
       </c>
       <c r="P36">
-        <v>12.546602206</v>
+        <v>12.428827115</v>
       </c>
       <c r="Q36">
-        <v>44.746602206</v>
+        <v>44.628827115</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1051774299791506</v>
+        <v>0.105982146712209</v>
       </c>
       <c r="T36">
-        <v>1.37130323277484</v>
+        <v>1.389887914831616</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.17</v>
       </c>
       <c r="W36">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.152824992045641</v>
+        <v>5.868946267277015</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4666,22 +4666,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08495304536293583</v>
+        <v>0.08488332693963228</v>
       </c>
       <c r="C37">
-        <v>101.0654309012358</v>
+        <v>99.52772275213982</v>
       </c>
       <c r="D37">
-        <v>150.4904309012358</v>
+        <v>150.5417227521398</v>
       </c>
       <c r="E37">
-        <v>-67.785</v>
+        <v>-66.196</v>
       </c>
       <c r="F37">
-        <v>55.61499999999999</v>
+        <v>57.204</v>
       </c>
       <c r="G37">
         <v>6.19</v>
@@ -4702,28 +4702,28 @@
         <v>18.05</v>
       </c>
       <c r="M37">
-        <v>3.0755095</v>
+        <v>3.1633812</v>
       </c>
       <c r="N37">
-        <v>14.9744905</v>
+        <v>14.8866188</v>
       </c>
       <c r="O37">
-        <v>2.545663385</v>
+        <v>2.530725196</v>
       </c>
       <c r="P37">
-        <v>12.428827115</v>
+        <v>12.355893604</v>
       </c>
       <c r="Q37">
-        <v>44.628827115</v>
+        <v>44.555893604</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.105982146712209</v>
+        <v>0.1068120108431754</v>
       </c>
       <c r="T37">
-        <v>1.389887914831616</v>
+        <v>1.409053368202666</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.868946267277015</v>
+        <v>5.705919982074874</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4748,22 +4748,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08488332693963227</v>
+        <v>0.08481360851632873</v>
       </c>
       <c r="C38">
-        <v>99.52772275213985</v>
+        <v>97.99004957870234</v>
       </c>
       <c r="D38">
-        <v>150.5417227521398</v>
+        <v>150.5930495787023</v>
       </c>
       <c r="E38">
-        <v>-66.196</v>
+        <v>-64.607</v>
       </c>
       <c r="F38">
-        <v>57.20399999999999</v>
+        <v>58.79299999999999</v>
       </c>
       <c r="G38">
         <v>6.19</v>
@@ -4784,28 +4784,28 @@
         <v>18.05</v>
       </c>
       <c r="M38">
-        <v>3.163381199999999</v>
+        <v>3.2512529</v>
       </c>
       <c r="N38">
-        <v>14.8866188</v>
+        <v>14.7987471</v>
       </c>
       <c r="O38">
-        <v>2.530725196</v>
+        <v>2.515787007</v>
       </c>
       <c r="P38">
-        <v>12.355893604</v>
+        <v>12.282960093</v>
       </c>
       <c r="Q38">
-        <v>44.555893604</v>
+        <v>44.482960093</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1068120108431754</v>
+        <v>0.1076682198671885</v>
       </c>
       <c r="T38">
-        <v>1.409053368202666</v>
+        <v>1.428827248664861</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.705919982074876</v>
+        <v>5.551705928505283</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4830,22 +4830,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08481360851632873</v>
+        <v>0.08474389009302517</v>
       </c>
       <c r="C39">
-        <v>97.99004957870234</v>
+        <v>96.45241141671004</v>
       </c>
       <c r="D39">
-        <v>150.5930495787023</v>
+        <v>150.64441141671</v>
       </c>
       <c r="E39">
-        <v>-64.607</v>
+        <v>-63.018</v>
       </c>
       <c r="F39">
-        <v>58.79299999999999</v>
+        <v>60.38199999999999</v>
       </c>
       <c r="G39">
         <v>6.19</v>
@@ -4866,28 +4866,28 @@
         <v>18.05</v>
       </c>
       <c r="M39">
-        <v>3.2512529</v>
+        <v>3.339124599999999</v>
       </c>
       <c r="N39">
-        <v>14.7987471</v>
+        <v>14.7108754</v>
       </c>
       <c r="O39">
-        <v>2.515787007</v>
+        <v>2.500848818</v>
       </c>
       <c r="P39">
-        <v>12.282960093</v>
+        <v>12.210026582</v>
       </c>
       <c r="Q39">
-        <v>44.482960093</v>
+        <v>44.410026582</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1076682198671885</v>
+        <v>0.1085520485371374</v>
       </c>
       <c r="T39">
-        <v>1.428827248664861</v>
+        <v>1.449238996238739</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.551705928505283</v>
+        <v>5.405608404070935</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4912,22 +4912,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08474389009302517</v>
+        <v>0.08467417166972162</v>
       </c>
       <c r="C40">
-        <v>96.45241141671004</v>
+        <v>94.91480830199856</v>
       </c>
       <c r="D40">
-        <v>150.64441141671</v>
+        <v>150.6958083019986</v>
       </c>
       <c r="E40">
-        <v>-63.018</v>
+        <v>-61.42899999999999</v>
       </c>
       <c r="F40">
-        <v>60.38199999999999</v>
+        <v>61.971</v>
       </c>
       <c r="G40">
         <v>6.19</v>
@@ -4948,28 +4948,28 @@
         <v>18.05</v>
       </c>
       <c r="M40">
-        <v>3.339124599999999</v>
+        <v>3.4269963</v>
       </c>
       <c r="N40">
-        <v>14.7108754</v>
+        <v>14.6230037</v>
       </c>
       <c r="O40">
-        <v>2.500848818</v>
+        <v>2.485910629</v>
       </c>
       <c r="P40">
-        <v>12.210026582</v>
+        <v>12.137093071</v>
       </c>
       <c r="Q40">
-        <v>44.410026582</v>
+        <v>44.337093071</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1085520485371374</v>
+        <v>0.1094648551962649</v>
       </c>
       <c r="T40">
-        <v>1.449238996238739</v>
+        <v>1.47031998143799</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.405608404070935</v>
+        <v>5.267003060376808</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4994,22 +4994,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08467417166972162</v>
+        <v>0.08460445324641808</v>
       </c>
       <c r="C41">
-        <v>94.91480830199856</v>
+        <v>93.37724027045246</v>
       </c>
       <c r="D41">
-        <v>150.6958083019986</v>
+        <v>150.7472402704525</v>
       </c>
       <c r="E41">
-        <v>-61.42899999999999</v>
+        <v>-59.84</v>
       </c>
       <c r="F41">
-        <v>61.971</v>
+        <v>63.56</v>
       </c>
       <c r="G41">
         <v>6.19</v>
@@ -5030,28 +5030,28 @@
         <v>18.05</v>
       </c>
       <c r="M41">
-        <v>3.4269963</v>
+        <v>3.514868</v>
       </c>
       <c r="N41">
-        <v>14.6230037</v>
+        <v>14.535132</v>
       </c>
       <c r="O41">
-        <v>2.485910629</v>
+        <v>2.47097244</v>
       </c>
       <c r="P41">
-        <v>12.137093071</v>
+        <v>12.06415956</v>
       </c>
       <c r="Q41">
-        <v>44.337093071</v>
+        <v>44.26415956</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1094648551962649</v>
+        <v>0.1104080887440301</v>
       </c>
       <c r="T41">
-        <v>1.47031998143799</v>
+        <v>1.492103666143883</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.267003060376808</v>
+        <v>5.135327983867388</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5076,22 +5076,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08460445324641808</v>
+        <v>0.08453473482311452</v>
       </c>
       <c r="C42">
-        <v>93.37724027045246</v>
+        <v>91.83970735800534</v>
       </c>
       <c r="D42">
-        <v>150.7472402704525</v>
+        <v>150.7987073580053</v>
       </c>
       <c r="E42">
-        <v>-59.84</v>
+        <v>-58.25099999999999</v>
       </c>
       <c r="F42">
-        <v>63.56</v>
+        <v>65.149</v>
       </c>
       <c r="G42">
         <v>6.19</v>
@@ -5112,28 +5112,28 @@
         <v>18.05</v>
       </c>
       <c r="M42">
-        <v>3.514868</v>
+        <v>3.6027397</v>
       </c>
       <c r="N42">
-        <v>14.535132</v>
+        <v>14.4472603</v>
       </c>
       <c r="O42">
-        <v>2.47097244</v>
+        <v>2.456034251</v>
       </c>
       <c r="P42">
-        <v>12.06415956</v>
+        <v>11.991226049</v>
       </c>
       <c r="Q42">
-        <v>44.26415956</v>
+        <v>44.191226049</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1104080887440301</v>
+        <v>0.1113832963103636</v>
       </c>
       <c r="T42">
-        <v>1.492103666143883</v>
+        <v>1.514625780839806</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.135327983867388</v>
+        <v>5.010076081821841</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5158,22 +5158,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08453473482311452</v>
+        <v>0.08446501639981097</v>
       </c>
       <c r="C43">
-        <v>91.83970735800534</v>
+        <v>90.3022096006398</v>
       </c>
       <c r="D43">
-        <v>150.7987073580053</v>
+        <v>150.8502096006398</v>
       </c>
       <c r="E43">
-        <v>-58.25099999999999</v>
+        <v>-56.66199999999999</v>
       </c>
       <c r="F43">
-        <v>65.149</v>
+        <v>66.738</v>
       </c>
       <c r="G43">
         <v>6.19</v>
@@ -5194,28 +5194,28 @@
         <v>18.05</v>
       </c>
       <c r="M43">
-        <v>3.6027397</v>
+        <v>3.6906114</v>
       </c>
       <c r="N43">
-        <v>14.4472603</v>
+        <v>14.3593886</v>
       </c>
       <c r="O43">
-        <v>2.456034251</v>
+        <v>2.441096062</v>
       </c>
       <c r="P43">
-        <v>11.991226049</v>
+        <v>11.918292538</v>
       </c>
       <c r="Q43">
-        <v>44.191226049</v>
+        <v>44.118292538</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1113832963103636</v>
+        <v>0.112392131723812</v>
       </c>
       <c r="T43">
-        <v>1.514625780839806</v>
+        <v>1.537924520180416</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.010076081821841</v>
+        <v>4.890788556064178</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5240,22 +5240,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08446501639981097</v>
+        <v>0.08439529797650744</v>
       </c>
       <c r="C44">
-        <v>90.30220960063981</v>
+        <v>88.76474703438767</v>
       </c>
       <c r="D44">
-        <v>150.8502096006398</v>
+        <v>150.9017470343877</v>
       </c>
       <c r="E44">
-        <v>-56.66200000000001</v>
+        <v>-55.07300000000001</v>
       </c>
       <c r="F44">
-        <v>66.73799999999999</v>
+        <v>68.32699999999998</v>
       </c>
       <c r="G44">
         <v>6.19</v>
@@ -5276,28 +5276,28 @@
         <v>18.05</v>
       </c>
       <c r="M44">
-        <v>3.690611399999999</v>
+        <v>3.778483099999999</v>
       </c>
       <c r="N44">
-        <v>14.3593886</v>
+        <v>14.2715169</v>
       </c>
       <c r="O44">
-        <v>2.441096062</v>
+        <v>2.426157873</v>
       </c>
       <c r="P44">
-        <v>11.918292538</v>
+        <v>11.845359027</v>
       </c>
       <c r="Q44">
-        <v>44.118292538</v>
+        <v>44.045359027</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.112392131723812</v>
+        <v>0.1134363648710656</v>
       </c>
       <c r="T44">
-        <v>1.537924520180416</v>
+        <v>1.562040759147012</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.890788556064179</v>
+        <v>4.777049287318501</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5322,22 +5322,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08439529797650744</v>
+        <v>0.08432557955320387</v>
       </c>
       <c r="C45">
-        <v>88.76474703438767</v>
+        <v>87.22731969533004</v>
       </c>
       <c r="D45">
-        <v>150.9017470343877</v>
+        <v>150.95331969533</v>
       </c>
       <c r="E45">
-        <v>-55.07300000000001</v>
+        <v>-53.48399999999999</v>
       </c>
       <c r="F45">
-        <v>68.32699999999998</v>
+        <v>69.916</v>
       </c>
       <c r="G45">
         <v>6.19</v>
@@ -5358,28 +5358,28 @@
         <v>18.05</v>
       </c>
       <c r="M45">
-        <v>3.778483099999999</v>
+        <v>3.8663548</v>
       </c>
       <c r="N45">
-        <v>14.2715169</v>
+        <v>14.1836452</v>
       </c>
       <c r="O45">
-        <v>2.426157873</v>
+        <v>2.411219684</v>
       </c>
       <c r="P45">
-        <v>11.845359027</v>
+        <v>11.772425516</v>
       </c>
       <c r="Q45">
-        <v>44.045359027</v>
+        <v>43.972425516</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1134363648710656</v>
+        <v>0.1145178920592926</v>
       </c>
       <c r="T45">
-        <v>1.562040759147012</v>
+        <v>1.587018292362416</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.777049287318501</v>
+        <v>4.668479985333989</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5404,22 +5404,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08432557955320387</v>
+        <v>0.0842558611299003</v>
       </c>
       <c r="C46">
-        <v>87.22731969533004</v>
+        <v>85.68992761959734</v>
       </c>
       <c r="D46">
-        <v>150.95331969533</v>
+        <v>151.0049276195973</v>
       </c>
       <c r="E46">
-        <v>-53.48399999999999</v>
+        <v>-51.895</v>
       </c>
       <c r="F46">
-        <v>69.916</v>
+        <v>71.505</v>
       </c>
       <c r="G46">
         <v>6.19</v>
@@ -5440,28 +5440,28 @@
         <v>18.05</v>
       </c>
       <c r="M46">
-        <v>3.8663548</v>
+        <v>3.9542265</v>
       </c>
       <c r="N46">
-        <v>14.1836452</v>
+        <v>14.0957735</v>
       </c>
       <c r="O46">
-        <v>2.411219684</v>
+        <v>2.396281495</v>
       </c>
       <c r="P46">
-        <v>11.772425516</v>
+        <v>11.699492005</v>
       </c>
       <c r="Q46">
-        <v>43.972425516</v>
+        <v>43.899492005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1145178920592926</v>
+        <v>0.1156387475089097</v>
       </c>
       <c r="T46">
-        <v>1.587018292362416</v>
+        <v>1.612904099512925</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.668479985333989</v>
+        <v>4.5647359856599</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5486,22 +5486,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0842558611299003</v>
+        <v>0.08514064270659676</v>
       </c>
       <c r="C47">
-        <v>85.68992761959734</v>
+        <v>83.44858891330412</v>
       </c>
       <c r="D47">
-        <v>151.0049276195973</v>
+        <v>150.3525889133041</v>
       </c>
       <c r="E47">
-        <v>-51.895</v>
+        <v>-50.306</v>
       </c>
       <c r="F47">
-        <v>71.505</v>
+        <v>73.09399999999999</v>
       </c>
       <c r="G47">
         <v>6.19</v>
@@ -5522,45 +5522,45 @@
         <v>18.05</v>
       </c>
       <c r="M47">
-        <v>3.9542265</v>
+        <v>4.2248332</v>
       </c>
       <c r="N47">
-        <v>14.0957735</v>
+        <v>13.8251668</v>
       </c>
       <c r="O47">
-        <v>2.396281495</v>
+        <v>2.350278356</v>
       </c>
       <c r="P47">
-        <v>11.699492005</v>
+        <v>11.474888444</v>
       </c>
       <c r="Q47">
-        <v>43.899492005</v>
+        <v>43.674888444</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1156387475089097</v>
+        <v>0.1168011161233273</v>
       </c>
       <c r="T47">
-        <v>1.612904099512925</v>
+        <v>1.639748640261601</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.17</v>
       </c>
       <c r="W47">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.5647359856599</v>
+        <v>4.27235801877338</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5568,22 +5568,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08514064270659676</v>
+        <v>0.08509167428329321</v>
       </c>
       <c r="C48">
-        <v>83.44858891330412</v>
+        <v>81.89554536577432</v>
       </c>
       <c r="D48">
-        <v>150.3525889133041</v>
+        <v>150.3885453657743</v>
       </c>
       <c r="E48">
-        <v>-50.306</v>
+        <v>-48.717</v>
       </c>
       <c r="F48">
-        <v>73.09399999999999</v>
+        <v>74.68299999999999</v>
       </c>
       <c r="G48">
         <v>6.19</v>
@@ -5604,28 +5604,28 @@
         <v>18.05</v>
       </c>
       <c r="M48">
-        <v>4.2248332</v>
+        <v>4.3166774</v>
       </c>
       <c r="N48">
-        <v>13.8251668</v>
+        <v>13.7333226</v>
       </c>
       <c r="O48">
-        <v>2.350278356</v>
+        <v>2.334664842</v>
       </c>
       <c r="P48">
-        <v>11.474888444</v>
+        <v>11.398657758</v>
       </c>
       <c r="Q48">
-        <v>43.674888444</v>
+        <v>43.598657758</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1168011161233273</v>
+        <v>0.1180073477043268</v>
       </c>
       <c r="T48">
-        <v>1.639748640261601</v>
+        <v>1.667606182547963</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.27235801877338</v>
+        <v>4.181456784331393</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5650,22 +5650,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08509167428329321</v>
+        <v>0.08504270585998966</v>
       </c>
       <c r="C49">
-        <v>81.89554536577432</v>
+        <v>80.34251902015296</v>
       </c>
       <c r="D49">
-        <v>150.3885453657743</v>
+        <v>150.424519020153</v>
       </c>
       <c r="E49">
-        <v>-48.717</v>
+        <v>-47.128</v>
       </c>
       <c r="F49">
-        <v>74.68299999999999</v>
+        <v>76.27199999999999</v>
       </c>
       <c r="G49">
         <v>6.19</v>
@@ -5686,28 +5686,28 @@
         <v>18.05</v>
       </c>
       <c r="M49">
-        <v>4.3166774</v>
+        <v>4.408521599999999</v>
       </c>
       <c r="N49">
-        <v>13.7333226</v>
+        <v>13.6414784</v>
       </c>
       <c r="O49">
-        <v>2.334664842</v>
+        <v>2.319051328</v>
       </c>
       <c r="P49">
-        <v>11.398657758</v>
+        <v>11.322427072</v>
       </c>
       <c r="Q49">
-        <v>43.598657758</v>
+        <v>43.522427072</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1180073477043268</v>
+        <v>0.1192599728076724</v>
       </c>
       <c r="T49">
-        <v>1.667606182547963</v>
+        <v>1.696535168768416</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.181456784331393</v>
+        <v>4.094343101324489</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5732,22 +5732,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08504270585998966</v>
+        <v>0.0849937374366861</v>
       </c>
       <c r="C50">
-        <v>80.34251902015296</v>
+        <v>78.78950988878731</v>
       </c>
       <c r="D50">
-        <v>150.424519020153</v>
+        <v>150.4605098887873</v>
       </c>
       <c r="E50">
-        <v>-47.128</v>
+        <v>-45.539</v>
       </c>
       <c r="F50">
-        <v>76.27199999999999</v>
+        <v>77.86099999999999</v>
       </c>
       <c r="G50">
         <v>6.19</v>
@@ -5768,28 +5768,28 @@
         <v>18.05</v>
       </c>
       <c r="M50">
-        <v>4.408521599999999</v>
+        <v>4.5003658</v>
       </c>
       <c r="N50">
-        <v>13.6414784</v>
+        <v>13.5496342</v>
       </c>
       <c r="O50">
-        <v>2.319051328</v>
+        <v>2.303437814</v>
       </c>
       <c r="P50">
-        <v>11.322427072</v>
+        <v>11.246196386</v>
       </c>
       <c r="Q50">
-        <v>43.522427072</v>
+        <v>43.446196386</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1192599728076724</v>
+        <v>0.1205617204640904</v>
       </c>
       <c r="T50">
-        <v>1.696535168768416</v>
+        <v>1.72659862503673</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.094343101324489</v>
+        <v>4.010785078848478</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5814,22 +5814,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0849937374366861</v>
+        <v>0.08639726901338256</v>
       </c>
       <c r="C51">
-        <v>78.78950988878731</v>
+        <v>76.17572151705366</v>
       </c>
       <c r="D51">
-        <v>150.4605098887873</v>
+        <v>149.4357215170537</v>
       </c>
       <c r="E51">
-        <v>-45.539</v>
+        <v>-43.95</v>
       </c>
       <c r="F51">
-        <v>77.86099999999999</v>
+        <v>79.44999999999999</v>
       </c>
       <c r="G51">
         <v>6.19</v>
@@ -5850,45 +5850,45 @@
         <v>18.05</v>
       </c>
       <c r="M51">
-        <v>4.5003658</v>
+        <v>4.870284999999999</v>
       </c>
       <c r="N51">
-        <v>13.5496342</v>
+        <v>13.179715</v>
       </c>
       <c r="O51">
-        <v>2.303437814</v>
+        <v>2.24055155</v>
       </c>
       <c r="P51">
-        <v>11.246196386</v>
+        <v>10.93916345</v>
       </c>
       <c r="Q51">
-        <v>43.446196386</v>
+        <v>43.13916345</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1205617204640904</v>
+        <v>0.1219155380267651</v>
       </c>
       <c r="T51">
-        <v>1.72659862503673</v>
+        <v>1.757864619555776</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.17</v>
       </c>
       <c r="W51">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.010785078848478</v>
+        <v>3.706148613479499</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5896,22 +5896,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08639726901338256</v>
+        <v>0.08637735059007899</v>
       </c>
       <c r="C52">
-        <v>76.17572151705366</v>
+        <v>74.60116729167839</v>
       </c>
       <c r="D52">
-        <v>149.4357215170537</v>
+        <v>149.4501672916784</v>
       </c>
       <c r="E52">
-        <v>-43.95</v>
+        <v>-42.361</v>
       </c>
       <c r="F52">
-        <v>79.44999999999999</v>
+        <v>81.03899999999999</v>
       </c>
       <c r="G52">
         <v>6.19</v>
@@ -5932,28 +5932,28 @@
         <v>18.05</v>
       </c>
       <c r="M52">
-        <v>4.870284999999999</v>
+        <v>4.967690699999999</v>
       </c>
       <c r="N52">
-        <v>13.179715</v>
+        <v>13.0823093</v>
       </c>
       <c r="O52">
-        <v>2.24055155</v>
+        <v>2.223992581</v>
       </c>
       <c r="P52">
-        <v>10.93916345</v>
+        <v>10.858316719</v>
       </c>
       <c r="Q52">
-        <v>43.13916345</v>
+        <v>43.058316719</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1219155380267651</v>
+        <v>0.1233246134491408</v>
       </c>
       <c r="T52">
-        <v>1.757864619555776</v>
+        <v>1.790406777116416</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.706148613479499</v>
+        <v>3.633479032823038</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5978,22 +5978,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08637735059007899</v>
+        <v>0.08635743216677544</v>
       </c>
       <c r="C53">
-        <v>74.60116729167839</v>
+        <v>73.02661585948508</v>
       </c>
       <c r="D53">
-        <v>149.4501672916784</v>
+        <v>149.4646158594851</v>
       </c>
       <c r="E53">
-        <v>-42.361</v>
+        <v>-40.77200000000001</v>
       </c>
       <c r="F53">
-        <v>81.03899999999999</v>
+        <v>82.62799999999999</v>
       </c>
       <c r="G53">
         <v>6.19</v>
@@ -6014,28 +6014,28 @@
         <v>18.05</v>
       </c>
       <c r="M53">
-        <v>4.967690699999999</v>
+        <v>5.065096399999999</v>
       </c>
       <c r="N53">
-        <v>13.0823093</v>
+        <v>12.9849036</v>
       </c>
       <c r="O53">
-        <v>2.223992581</v>
+        <v>2.207433612</v>
       </c>
       <c r="P53">
-        <v>10.858316719</v>
+        <v>10.777469988</v>
       </c>
       <c r="Q53">
-        <v>43.058316719</v>
+        <v>42.977469988</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1233246134491408</v>
+        <v>0.1247924003474488</v>
       </c>
       <c r="T53">
-        <v>1.790406777116416</v>
+        <v>1.82430485790875</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.633479032823038</v>
+        <v>3.56360443603798</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6060,22 +6060,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08635743216677544</v>
+        <v>0.08756923374347189</v>
       </c>
       <c r="C54">
-        <v>73.02661585948508</v>
+        <v>70.56364606838862</v>
       </c>
       <c r="D54">
-        <v>149.4646158594851</v>
+        <v>148.5906460683886</v>
       </c>
       <c r="E54">
-        <v>-40.77200000000001</v>
+        <v>-39.18299999999999</v>
       </c>
       <c r="F54">
-        <v>82.62799999999999</v>
+        <v>84.217</v>
       </c>
       <c r="G54">
         <v>6.19</v>
@@ -6096,45 +6096,45 @@
         <v>18.05</v>
       </c>
       <c r="M54">
-        <v>5.065096399999999</v>
+        <v>5.3983097</v>
       </c>
       <c r="N54">
-        <v>12.9849036</v>
+        <v>12.6516903</v>
       </c>
       <c r="O54">
-        <v>2.207433612</v>
+        <v>2.150787351</v>
       </c>
       <c r="P54">
-        <v>10.777469988</v>
+        <v>10.500902949</v>
       </c>
       <c r="Q54">
-        <v>42.977469988</v>
+        <v>42.700902949</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1247924003474488</v>
+        <v>0.1263226462627062</v>
       </c>
       <c r="T54">
-        <v>1.82430485790875</v>
+        <v>1.859645410224161</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.17</v>
       </c>
       <c r="W54">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.56360443603798</v>
+        <v>3.343639213585689</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6142,22 +6142,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08756923374347189</v>
+        <v>0.08757255532016833</v>
       </c>
       <c r="C55">
-        <v>70.56364606838862</v>
+        <v>68.97226454246571</v>
       </c>
       <c r="D55">
-        <v>148.5906460683886</v>
+        <v>148.5882645424657</v>
       </c>
       <c r="E55">
-        <v>-39.18299999999999</v>
+        <v>-37.59399999999999</v>
       </c>
       <c r="F55">
-        <v>84.217</v>
+        <v>85.806</v>
       </c>
       <c r="G55">
         <v>6.19</v>
@@ -6178,28 +6178,28 @@
         <v>18.05</v>
       </c>
       <c r="M55">
-        <v>5.3983097</v>
+        <v>5.500164600000001</v>
       </c>
       <c r="N55">
-        <v>12.6516903</v>
+        <v>12.5498354</v>
       </c>
       <c r="O55">
-        <v>2.150787351</v>
+        <v>2.133472018</v>
       </c>
       <c r="P55">
-        <v>10.500902949</v>
+        <v>10.416363382</v>
       </c>
       <c r="Q55">
-        <v>42.700902949</v>
+        <v>42.616363382</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1263226462627062</v>
+        <v>0.1279194246090616</v>
       </c>
       <c r="T55">
-        <v>1.859645410224161</v>
+        <v>1.896522508292416</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.343639213585689</v>
+        <v>3.281719968889657</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6224,22 +6224,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08757255532016833</v>
+        <v>0.08757587689686479</v>
       </c>
       <c r="C56">
-        <v>68.97226454246571</v>
+        <v>67.38088309288104</v>
       </c>
       <c r="D56">
-        <v>148.5882645424657</v>
+        <v>148.585883092881</v>
       </c>
       <c r="E56">
-        <v>-37.59399999999999</v>
+        <v>-36.005</v>
       </c>
       <c r="F56">
-        <v>85.806</v>
+        <v>87.395</v>
       </c>
       <c r="G56">
         <v>6.19</v>
@@ -6260,28 +6260,28 @@
         <v>18.05</v>
       </c>
       <c r="M56">
-        <v>5.500164600000001</v>
+        <v>5.6020195</v>
       </c>
       <c r="N56">
-        <v>12.5498354</v>
+        <v>12.4479805</v>
       </c>
       <c r="O56">
-        <v>2.133472018</v>
+        <v>2.116156685</v>
       </c>
       <c r="P56">
-        <v>10.416363382</v>
+        <v>10.331823815</v>
       </c>
       <c r="Q56">
-        <v>42.616363382</v>
+        <v>42.531823815</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1279194246090616</v>
+        <v>0.1295871708819218</v>
       </c>
       <c r="T56">
-        <v>1.896522508292416</v>
+        <v>1.935038588497039</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.281719968889657</v>
+        <v>3.222052333091664</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6306,22 +6306,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08757587689686479</v>
+        <v>0.08757919847356124</v>
       </c>
       <c r="C57">
-        <v>67.38088309288104</v>
+        <v>65.78950171963093</v>
       </c>
       <c r="D57">
-        <v>148.585883092881</v>
+        <v>148.5835017196309</v>
       </c>
       <c r="E57">
-        <v>-36.005</v>
+        <v>-34.416</v>
       </c>
       <c r="F57">
-        <v>87.395</v>
+        <v>88.98399999999999</v>
       </c>
       <c r="G57">
         <v>6.19</v>
@@ -6342,28 +6342,28 @@
         <v>18.05</v>
       </c>
       <c r="M57">
-        <v>5.6020195</v>
+        <v>5.7038744</v>
       </c>
       <c r="N57">
-        <v>12.4479805</v>
+        <v>12.3461256</v>
       </c>
       <c r="O57">
-        <v>2.116156685</v>
+        <v>2.098841352</v>
       </c>
       <c r="P57">
-        <v>10.331823815</v>
+        <v>10.247284248</v>
       </c>
       <c r="Q57">
-        <v>42.531823815</v>
+        <v>42.447284248</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1295871708819218</v>
+        <v>0.1313307238035483</v>
       </c>
       <c r="T57">
-        <v>1.935038588497039</v>
+        <v>1.975305399620052</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.222052333091664</v>
+        <v>3.164515684286456</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6388,22 +6388,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08757919847356124</v>
+        <v>0.08758252005025768</v>
       </c>
       <c r="C58">
-        <v>65.78950171963093</v>
+        <v>64.19812042271177</v>
       </c>
       <c r="D58">
-        <v>148.5835017196309</v>
+        <v>148.5811204227118</v>
       </c>
       <c r="E58">
-        <v>-34.416</v>
+        <v>-32.827</v>
       </c>
       <c r="F58">
-        <v>88.98399999999999</v>
+        <v>90.57299999999999</v>
       </c>
       <c r="G58">
         <v>6.19</v>
@@ -6424,28 +6424,28 @@
         <v>18.05</v>
       </c>
       <c r="M58">
-        <v>5.7038744</v>
+        <v>5.8057293</v>
       </c>
       <c r="N58">
-        <v>12.3461256</v>
+        <v>12.2442707</v>
       </c>
       <c r="O58">
-        <v>2.098841352</v>
+        <v>2.081526019</v>
       </c>
       <c r="P58">
-        <v>10.247284248</v>
+        <v>10.162744681</v>
       </c>
       <c r="Q58">
-        <v>42.447284248</v>
+        <v>42.362744681</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1313307238035483</v>
+        <v>0.1331553722099016</v>
       </c>
       <c r="T58">
-        <v>1.975305399620052</v>
+        <v>2.017445085679021</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.164515684286456</v>
+        <v>3.108997865263886</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6470,22 +6470,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08758252005025768</v>
+        <v>0.08758584162695413</v>
       </c>
       <c r="C59">
-        <v>64.19812042271177</v>
+        <v>62.60673920211981</v>
       </c>
       <c r="D59">
-        <v>148.5811204227118</v>
+        <v>148.5787392021198</v>
       </c>
       <c r="E59">
-        <v>-32.827</v>
+        <v>-31.238</v>
       </c>
       <c r="F59">
-        <v>90.57299999999999</v>
+        <v>92.16199999999999</v>
       </c>
       <c r="G59">
         <v>6.19</v>
@@ -6506,28 +6506,28 @@
         <v>18.05</v>
       </c>
       <c r="M59">
-        <v>5.8057293</v>
+        <v>5.9075842</v>
       </c>
       <c r="N59">
-        <v>12.2442707</v>
+        <v>12.1424158</v>
       </c>
       <c r="O59">
-        <v>2.081526019</v>
+        <v>2.064210686</v>
       </c>
       <c r="P59">
-        <v>10.162744681</v>
+        <v>10.078205114</v>
       </c>
       <c r="Q59">
-        <v>42.362744681</v>
+        <v>42.278205114</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1331553722099016</v>
+        <v>0.1350669086356051</v>
       </c>
       <c r="T59">
-        <v>2.017445085679021</v>
+        <v>2.061591423455083</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.108997865263886</v>
+        <v>3.05539445379382</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6552,22 +6552,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08758584162695414</v>
+        <v>0.08758916320365057</v>
       </c>
       <c r="C60">
-        <v>62.60673920211983</v>
+        <v>61.01535805785144</v>
       </c>
       <c r="D60">
-        <v>148.5787392021198</v>
+        <v>148.5763580578514</v>
       </c>
       <c r="E60">
-        <v>-31.23800000000001</v>
+        <v>-29.64900000000002</v>
       </c>
       <c r="F60">
-        <v>92.16199999999998</v>
+        <v>93.75099999999998</v>
       </c>
       <c r="G60">
         <v>6.19</v>
@@ -6588,28 +6588,28 @@
         <v>18.05</v>
       </c>
       <c r="M60">
-        <v>5.907584199999999</v>
+        <v>6.009439099999999</v>
       </c>
       <c r="N60">
-        <v>12.1424158</v>
+        <v>12.0405609</v>
       </c>
       <c r="O60">
-        <v>2.064210686</v>
+        <v>2.046895353</v>
       </c>
       <c r="P60">
-        <v>10.078205114</v>
+        <v>9.993665546999999</v>
       </c>
       <c r="Q60">
-        <v>42.278205114</v>
+        <v>42.193665547</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1350669086356051</v>
+        <v>0.1370716907406112</v>
       </c>
       <c r="T60">
-        <v>2.061591423455083</v>
+        <v>2.10789124112266</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.05539445379382</v>
+        <v>3.003608107119348</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6634,22 +6634,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08758916320365057</v>
+        <v>0.09147688478034702</v>
       </c>
       <c r="C61">
-        <v>61.01535805785144</v>
+        <v>56.69071954742238</v>
       </c>
       <c r="D61">
-        <v>148.5763580578514</v>
+        <v>145.8407195474224</v>
       </c>
       <c r="E61">
-        <v>-29.64900000000002</v>
+        <v>-28.06</v>
       </c>
       <c r="F61">
-        <v>93.75099999999998</v>
+        <v>95.33999999999999</v>
       </c>
       <c r="G61">
         <v>6.19</v>
@@ -6670,45 +6670,45 @@
         <v>18.05</v>
       </c>
       <c r="M61">
-        <v>6.009439099999999</v>
+        <v>6.854946</v>
       </c>
       <c r="N61">
-        <v>12.0405609</v>
+        <v>11.195054</v>
       </c>
       <c r="O61">
-        <v>2.046895353</v>
+        <v>1.90315918</v>
       </c>
       <c r="P61">
-        <v>9.993665546999999</v>
+        <v>9.291894819999998</v>
       </c>
       <c r="Q61">
-        <v>42.193665547</v>
+        <v>41.49189482</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1370716907406112</v>
+        <v>0.1391767119508676</v>
       </c>
       <c r="T61">
-        <v>2.10789124112266</v>
+        <v>2.156506049673616</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.17</v>
       </c>
       <c r="W61">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.003608107119348</v>
+        <v>2.633135257374748</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6716,22 +6716,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09147688478034702</v>
+        <v>0.09154494635704347</v>
       </c>
       <c r="C62">
-        <v>56.69071954742238</v>
+        <v>55.05472421988132</v>
       </c>
       <c r="D62">
-        <v>145.8407195474224</v>
+        <v>145.7937242198813</v>
       </c>
       <c r="E62">
-        <v>-28.06</v>
+        <v>-26.471</v>
       </c>
       <c r="F62">
-        <v>95.33999999999999</v>
+        <v>96.92899999999999</v>
       </c>
       <c r="G62">
         <v>6.19</v>
@@ -6752,28 +6752,28 @@
         <v>18.05</v>
       </c>
       <c r="M62">
-        <v>6.854946</v>
+        <v>6.969195099999999</v>
       </c>
       <c r="N62">
-        <v>11.195054</v>
+        <v>11.0808049</v>
       </c>
       <c r="O62">
-        <v>1.90315918</v>
+        <v>1.883736832999999</v>
       </c>
       <c r="P62">
-        <v>9.291894819999998</v>
+        <v>9.197068066999996</v>
       </c>
       <c r="Q62">
-        <v>41.49189482</v>
+        <v>41.397068067</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1391767119508676</v>
+        <v>0.1413896829667781</v>
       </c>
       <c r="T62">
-        <v>2.156506049673616</v>
+        <v>2.207613925329749</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.633135257374748</v>
+        <v>2.589969105614506</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6798,22 +6798,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09154494635704347</v>
+        <v>0.09161300793373992</v>
       </c>
       <c r="C63">
-        <v>55.05472421988132</v>
+        <v>53.41875916988373</v>
       </c>
       <c r="D63">
-        <v>145.7937242198813</v>
+        <v>145.7467591698837</v>
       </c>
       <c r="E63">
-        <v>-26.471</v>
+        <v>-24.88200000000001</v>
       </c>
       <c r="F63">
-        <v>96.92899999999999</v>
+        <v>98.51799999999999</v>
       </c>
       <c r="G63">
         <v>6.19</v>
@@ -6834,28 +6834,28 @@
         <v>18.05</v>
       </c>
       <c r="M63">
-        <v>6.969195099999999</v>
+        <v>7.0834442</v>
       </c>
       <c r="N63">
-        <v>11.0808049</v>
+        <v>10.9665558</v>
       </c>
       <c r="O63">
-        <v>1.883736832999999</v>
+        <v>1.864314486</v>
       </c>
       <c r="P63">
-        <v>9.197068066999996</v>
+        <v>9.102241313999999</v>
       </c>
       <c r="Q63">
-        <v>41.397068067</v>
+        <v>41.302241314</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1413896829667781</v>
+        <v>0.1437191261414208</v>
       </c>
       <c r="T63">
-        <v>2.207613925329749</v>
+        <v>2.26141168917831</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.589969105614506</v>
+        <v>2.548195410362659</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6880,22 +6880,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09161300793373992</v>
+        <v>0.09168106951043636</v>
       </c>
       <c r="C64">
-        <v>53.41875916988373</v>
+        <v>51.78282436817871</v>
       </c>
       <c r="D64">
-        <v>145.7467591698837</v>
+        <v>145.6998243681787</v>
       </c>
       <c r="E64">
-        <v>-24.88200000000001</v>
+        <v>-23.29300000000001</v>
       </c>
       <c r="F64">
-        <v>98.51799999999999</v>
+        <v>100.107</v>
       </c>
       <c r="G64">
         <v>6.19</v>
@@ -6916,28 +6916,28 @@
         <v>18.05</v>
       </c>
       <c r="M64">
-        <v>7.0834442</v>
+        <v>7.197693299999999</v>
       </c>
       <c r="N64">
-        <v>10.9665558</v>
+        <v>10.8523067</v>
       </c>
       <c r="O64">
-        <v>1.864314486</v>
+        <v>1.844892139</v>
       </c>
       <c r="P64">
-        <v>9.102241313999999</v>
+        <v>9.007414560999997</v>
       </c>
       <c r="Q64">
-        <v>41.302241314</v>
+        <v>41.207414561</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1437191261414208</v>
+        <v>0.1461744851633415</v>
       </c>
       <c r="T64">
-        <v>2.26141168917831</v>
+        <v>2.318117440261929</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.548195410362659</v>
+        <v>2.507747864166427</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6962,22 +6962,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09168106951043636</v>
+        <v>0.0938208110871328</v>
       </c>
       <c r="C65">
-        <v>51.78282436817871</v>
+        <v>48.7335323671778</v>
       </c>
       <c r="D65">
-        <v>145.6998243681787</v>
+        <v>144.2395323671778</v>
       </c>
       <c r="E65">
-        <v>-23.29300000000001</v>
+        <v>-21.70400000000001</v>
       </c>
       <c r="F65">
-        <v>100.107</v>
+        <v>101.696</v>
       </c>
       <c r="G65">
         <v>6.19</v>
@@ -6998,45 +6998,45 @@
         <v>18.05</v>
       </c>
       <c r="M65">
-        <v>7.197693299999999</v>
+        <v>7.708556799999999</v>
       </c>
       <c r="N65">
-        <v>10.8523067</v>
+        <v>10.3414432</v>
       </c>
       <c r="O65">
-        <v>1.844892139</v>
+        <v>1.758045344</v>
       </c>
       <c r="P65">
-        <v>9.007414560999997</v>
+        <v>8.583397855999998</v>
       </c>
       <c r="Q65">
-        <v>41.207414561</v>
+        <v>40.783397856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1461744851633415</v>
+        <v>0.1487662530198134</v>
       </c>
       <c r="T65">
-        <v>2.318117440261929</v>
+        <v>2.377973510850193</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.17</v>
       </c>
       <c r="W65">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.507747864166427</v>
+        <v>2.341553739345866</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7044,22 +7044,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0938208110871328</v>
+        <v>0.09392124266382926</v>
       </c>
       <c r="C66">
-        <v>48.7335323671778</v>
+        <v>47.07671050896734</v>
       </c>
       <c r="D66">
-        <v>144.2395323671778</v>
+        <v>144.1717105089673</v>
       </c>
       <c r="E66">
-        <v>-21.70400000000001</v>
+        <v>-20.11500000000001</v>
       </c>
       <c r="F66">
-        <v>101.696</v>
+        <v>103.285</v>
       </c>
       <c r="G66">
         <v>6.19</v>
@@ -7080,28 +7080,28 @@
         <v>18.05</v>
       </c>
       <c r="M66">
-        <v>7.708556799999999</v>
+        <v>7.829002999999999</v>
       </c>
       <c r="N66">
-        <v>10.3414432</v>
+        <v>10.220997</v>
       </c>
       <c r="O66">
-        <v>1.758045344</v>
+        <v>1.73756949</v>
       </c>
       <c r="P66">
-        <v>8.583397855999998</v>
+        <v>8.483427509999997</v>
       </c>
       <c r="Q66">
-        <v>40.783397856</v>
+        <v>40.68342751</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1487662530198134</v>
+        <v>0.151506121896655</v>
       </c>
       <c r="T66">
-        <v>2.377973510850193</v>
+        <v>2.441249928329216</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.341553739345866</v>
+        <v>2.305529835663621</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7126,22 +7126,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09392124266382926</v>
+        <v>0.09402167424052571</v>
       </c>
       <c r="C67">
-        <v>47.07671050896734</v>
+        <v>45.41995240086129</v>
       </c>
       <c r="D67">
-        <v>144.1717105089673</v>
+        <v>144.1039524008613</v>
       </c>
       <c r="E67">
-        <v>-20.11500000000001</v>
+        <v>-18.526</v>
       </c>
       <c r="F67">
-        <v>103.285</v>
+        <v>104.874</v>
       </c>
       <c r="G67">
         <v>6.19</v>
@@ -7162,28 +7162,28 @@
         <v>18.05</v>
       </c>
       <c r="M67">
-        <v>7.829002999999999</v>
+        <v>7.9494492</v>
       </c>
       <c r="N67">
-        <v>10.220997</v>
+        <v>10.1005508</v>
       </c>
       <c r="O67">
-        <v>1.73756949</v>
+        <v>1.717093636</v>
       </c>
       <c r="P67">
-        <v>8.483427509999997</v>
+        <v>8.383457163999998</v>
       </c>
       <c r="Q67">
-        <v>40.68342751</v>
+        <v>40.583457164</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.151506121896655</v>
+        <v>0.154407159530958</v>
       </c>
       <c r="T67">
-        <v>2.441249928329216</v>
+        <v>2.508248488012887</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.305529835663621</v>
+        <v>2.270597565426294</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7208,22 +7208,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09402167424052571</v>
+        <v>0.09412210581722216</v>
       </c>
       <c r="C68">
-        <v>45.41995240086129</v>
+        <v>43.7632579530177</v>
       </c>
       <c r="D68">
-        <v>144.1039524008613</v>
+        <v>144.0362579530177</v>
       </c>
       <c r="E68">
-        <v>-18.526</v>
+        <v>-16.937</v>
       </c>
       <c r="F68">
-        <v>104.874</v>
+        <v>106.463</v>
       </c>
       <c r="G68">
         <v>6.19</v>
@@ -7244,28 +7244,28 @@
         <v>18.05</v>
       </c>
       <c r="M68">
-        <v>7.9494492</v>
+        <v>8.0698954</v>
       </c>
       <c r="N68">
-        <v>10.1005508</v>
+        <v>9.980104599999997</v>
       </c>
       <c r="O68">
-        <v>1.717093636</v>
+        <v>1.696617782</v>
       </c>
       <c r="P68">
-        <v>8.383457163999998</v>
+        <v>8.283486817999997</v>
       </c>
       <c r="Q68">
-        <v>40.583457164</v>
+        <v>40.483486818</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.154407159530958</v>
+        <v>0.1574840176279459</v>
       </c>
       <c r="T68">
-        <v>2.508248488012887</v>
+        <v>2.579307566465264</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.270597565426294</v>
+        <v>2.236708049524409</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7290,22 +7290,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09412210581722216</v>
+        <v>0.09422253739391862</v>
       </c>
       <c r="C69">
-        <v>43.7632579530177</v>
+        <v>42.10662707576333</v>
       </c>
       <c r="D69">
-        <v>144.0362579530177</v>
+        <v>143.9686270757633</v>
       </c>
       <c r="E69">
-        <v>-16.937</v>
+        <v>-15.348</v>
       </c>
       <c r="F69">
-        <v>106.463</v>
+        <v>108.052</v>
       </c>
       <c r="G69">
         <v>6.19</v>
@@ -7326,28 +7326,28 @@
         <v>18.05</v>
       </c>
       <c r="M69">
-        <v>8.0698954</v>
+        <v>8.1903416</v>
       </c>
       <c r="N69">
-        <v>9.980104599999997</v>
+        <v>9.859658399999997</v>
       </c>
       <c r="O69">
-        <v>1.696617782</v>
+        <v>1.676141928</v>
       </c>
       <c r="P69">
-        <v>8.283486817999997</v>
+        <v>8.183516471999997</v>
       </c>
       <c r="Q69">
-        <v>40.483486818</v>
+        <v>40.383516472</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1574840176279459</v>
+        <v>0.1607531793559957</v>
       </c>
       <c r="T69">
-        <v>2.579307566465264</v>
+        <v>2.654807837320916</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.236708049524409</v>
+        <v>2.203815284090226</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7372,22 +7372,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09422253739391862</v>
+        <v>0.09432296897061504</v>
       </c>
       <c r="C70">
-        <v>42.10662707576333</v>
+        <v>40.45005967959332</v>
       </c>
       <c r="D70">
-        <v>143.9686270757633</v>
+        <v>143.9010596795933</v>
       </c>
       <c r="E70">
-        <v>-15.348</v>
+        <v>-13.759</v>
       </c>
       <c r="F70">
-        <v>108.052</v>
+        <v>109.641</v>
       </c>
       <c r="G70">
         <v>6.19</v>
@@ -7408,28 +7408,28 @@
         <v>18.05</v>
       </c>
       <c r="M70">
-        <v>8.1903416</v>
+        <v>8.3107878</v>
       </c>
       <c r="N70">
-        <v>9.859658399999997</v>
+        <v>9.739212199999997</v>
       </c>
       <c r="O70">
-        <v>1.676141928</v>
+        <v>1.655666074</v>
       </c>
       <c r="P70">
-        <v>8.183516471999997</v>
+        <v>8.083546125999998</v>
       </c>
       <c r="Q70">
-        <v>40.383516472</v>
+        <v>40.283546126</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1607531793559957</v>
+        <v>0.1642332547439195</v>
       </c>
       <c r="T70">
-        <v>2.654807837320916</v>
+        <v>2.735179093393061</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.203815284090226</v>
+        <v>2.171875932146889</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7454,22 +7454,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09432296897061504</v>
+        <v>0.09442340054731149</v>
       </c>
       <c r="C71">
-        <v>40.45005967959332</v>
+        <v>38.79355567517061</v>
       </c>
       <c r="D71">
-        <v>143.9010596795933</v>
+        <v>143.8335556751706</v>
       </c>
       <c r="E71">
-        <v>-13.759</v>
+        <v>-12.17</v>
       </c>
       <c r="F71">
-        <v>109.641</v>
+        <v>111.23</v>
       </c>
       <c r="G71">
         <v>6.19</v>
@@ -7490,28 +7490,28 @@
         <v>18.05</v>
       </c>
       <c r="M71">
-        <v>8.3107878</v>
+        <v>8.431234</v>
       </c>
       <c r="N71">
-        <v>9.739212199999997</v>
+        <v>9.618765999999997</v>
       </c>
       <c r="O71">
-        <v>1.655666074</v>
+        <v>1.63519022</v>
       </c>
       <c r="P71">
-        <v>8.083546125999998</v>
+        <v>7.983575779999997</v>
       </c>
       <c r="Q71">
-        <v>40.283546126</v>
+        <v>40.18357578</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1642332547439195</v>
+        <v>0.167945335157705</v>
       </c>
       <c r="T71">
-        <v>2.735179093393061</v>
+        <v>2.820908433203349</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.171875932146889</v>
+        <v>2.14084913311622</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7536,22 +7536,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09442340054731149</v>
+        <v>0.09452383212400796</v>
       </c>
       <c r="C72">
-        <v>38.79355567517061</v>
+        <v>37.13711497332586</v>
       </c>
       <c r="D72">
-        <v>143.8335556751706</v>
+        <v>143.7661149733259</v>
       </c>
       <c r="E72">
-        <v>-12.17</v>
+        <v>-10.58099999999999</v>
       </c>
       <c r="F72">
-        <v>111.23</v>
+        <v>112.819</v>
       </c>
       <c r="G72">
         <v>6.19</v>
@@ -7572,28 +7572,28 @@
         <v>18.05</v>
       </c>
       <c r="M72">
-        <v>8.431234</v>
+        <v>8.551680200000002</v>
       </c>
       <c r="N72">
-        <v>9.618765999999997</v>
+        <v>9.498319799999996</v>
       </c>
       <c r="O72">
-        <v>1.63519022</v>
+        <v>1.614714365999999</v>
       </c>
       <c r="P72">
-        <v>7.983575779999997</v>
+        <v>7.883605433999996</v>
       </c>
       <c r="Q72">
-        <v>40.18357578</v>
+        <v>40.083605434</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.167945335157705</v>
+        <v>0.1719134211172688</v>
       </c>
       <c r="T72">
-        <v>2.820908433203349</v>
+        <v>2.912550141276417</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.14084913311622</v>
+        <v>2.110696328424441</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7618,22 +7618,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09452383212400794</v>
+        <v>0.0946242637007044</v>
       </c>
       <c r="C73">
-        <v>37.13711497332589</v>
+        <v>35.48073748505688</v>
       </c>
       <c r="D73">
-        <v>143.7661149733259</v>
+        <v>143.6987374850569</v>
       </c>
       <c r="E73">
-        <v>-10.58100000000002</v>
+        <v>-8.992000000000019</v>
       </c>
       <c r="F73">
-        <v>112.819</v>
+        <v>114.408</v>
       </c>
       <c r="G73">
         <v>6.19</v>
@@ -7654,28 +7654,28 @@
         <v>18.05</v>
       </c>
       <c r="M73">
-        <v>8.551680199999998</v>
+        <v>8.672126399999998</v>
       </c>
       <c r="N73">
-        <v>9.498319799999999</v>
+        <v>9.377873599999999</v>
       </c>
       <c r="O73">
-        <v>1.614714366</v>
+        <v>1.594238512</v>
       </c>
       <c r="P73">
-        <v>7.883605433999999</v>
+        <v>7.783635087999999</v>
       </c>
       <c r="Q73">
-        <v>40.083605434</v>
+        <v>39.983635088</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1719134211172688</v>
+        <v>0.17616494178823</v>
       </c>
       <c r="T73">
-        <v>2.912550141276415</v>
+        <v>3.010737685640415</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.110696328424442</v>
+        <v>2.08138110164077</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7700,22 +7700,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0946242637007044</v>
+        <v>0.09472469527740084</v>
       </c>
       <c r="C74">
-        <v>35.48073748505688</v>
+        <v>33.8244231215281</v>
       </c>
       <c r="D74">
-        <v>143.6987374850569</v>
+        <v>143.6314231215281</v>
       </c>
       <c r="E74">
-        <v>-8.992000000000019</v>
+        <v>-7.403000000000006</v>
       </c>
       <c r="F74">
-        <v>114.408</v>
+        <v>115.997</v>
       </c>
       <c r="G74">
         <v>6.19</v>
@@ -7736,28 +7736,28 @@
         <v>18.05</v>
       </c>
       <c r="M74">
-        <v>8.672126399999998</v>
+        <v>8.7925726</v>
       </c>
       <c r="N74">
-        <v>9.377873599999999</v>
+        <v>9.257427399999997</v>
       </c>
       <c r="O74">
-        <v>1.594238512</v>
+        <v>1.573762658</v>
       </c>
       <c r="P74">
-        <v>7.783635087999999</v>
+        <v>7.683664741999998</v>
       </c>
       <c r="Q74">
-        <v>39.983635088</v>
+        <v>39.883664742</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.17616494178823</v>
+        <v>0.1807313899162994</v>
       </c>
       <c r="T74">
-        <v>3.010737685640415</v>
+        <v>3.116198381438785</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.08138110164077</v>
+        <v>2.052869031755279</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09472469527740084</v>
+        <v>0.09482512685409729</v>
       </c>
       <c r="C75">
-        <v>33.8244231215281</v>
+        <v>32.1681717940705</v>
       </c>
       <c r="D75">
-        <v>143.6314231215281</v>
+        <v>143.5641717940705</v>
       </c>
       <c r="E75">
-        <v>-7.403000000000006</v>
+        <v>-5.814000000000007</v>
       </c>
       <c r="F75">
-        <v>115.997</v>
+        <v>117.586</v>
       </c>
       <c r="G75">
         <v>6.19</v>
@@ -7818,28 +7818,28 @@
         <v>18.05</v>
       </c>
       <c r="M75">
-        <v>8.7925726</v>
+        <v>8.9130188</v>
       </c>
       <c r="N75">
-        <v>9.257427399999997</v>
+        <v>9.136981199999997</v>
       </c>
       <c r="O75">
-        <v>1.573762658</v>
+        <v>1.553286804</v>
       </c>
       <c r="P75">
-        <v>7.683664741999998</v>
+        <v>7.583694395999998</v>
       </c>
       <c r="Q75">
-        <v>39.883664742</v>
+        <v>39.783694396</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1807313899162994</v>
+        <v>0.1856491032849896</v>
       </c>
       <c r="T75">
-        <v>3.116198381438785</v>
+        <v>3.229771438452415</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.052869031755279</v>
+        <v>2.025127558353181</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7864,22 +7864,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09482512685409729</v>
+        <v>0.1037650584307937</v>
       </c>
       <c r="C76">
-        <v>32.1681717940705</v>
+        <v>24.83499825863794</v>
       </c>
       <c r="D76">
-        <v>143.5641717940705</v>
+        <v>137.8199982586379</v>
       </c>
       <c r="E76">
-        <v>-5.814000000000007</v>
+        <v>-4.225000000000009</v>
       </c>
       <c r="F76">
-        <v>117.586</v>
+        <v>119.175</v>
       </c>
       <c r="G76">
         <v>6.19</v>
@@ -7900,45 +7900,45 @@
         <v>18.05</v>
       </c>
       <c r="M76">
-        <v>8.9130188</v>
+        <v>10.72575</v>
       </c>
       <c r="N76">
-        <v>9.136981199999997</v>
+        <v>7.324249999999999</v>
       </c>
       <c r="O76">
-        <v>1.553286804</v>
+        <v>1.2451225</v>
       </c>
       <c r="P76">
-        <v>7.583694395999998</v>
+        <v>6.079127499999999</v>
       </c>
       <c r="Q76">
-        <v>39.783694396</v>
+        <v>38.2791275</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1856491032849896</v>
+        <v>0.190960233723175</v>
       </c>
       <c r="T76">
-        <v>3.229771438452415</v>
+        <v>3.352430340027135</v>
       </c>
       <c r="U76">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
         <v>0.17</v>
       </c>
       <c r="W76">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.025127558353181</v>
+        <v>1.682866000046617</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7946,22 +7946,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1037650584307937</v>
+        <v>0.1039833500074902</v>
       </c>
       <c r="C77">
-        <v>24.83499825863794</v>
+        <v>23.11148273198168</v>
       </c>
       <c r="D77">
-        <v>137.8199982586379</v>
+        <v>137.6854827319817</v>
       </c>
       <c r="E77">
-        <v>-4.225000000000009</v>
+        <v>-2.63600000000001</v>
       </c>
       <c r="F77">
-        <v>119.175</v>
+        <v>120.764</v>
       </c>
       <c r="G77">
         <v>6.19</v>
@@ -7982,28 +7982,28 @@
         <v>18.05</v>
       </c>
       <c r="M77">
-        <v>10.72575</v>
+        <v>10.86876</v>
       </c>
       <c r="N77">
-        <v>7.324249999999999</v>
+        <v>7.181239999999999</v>
       </c>
       <c r="O77">
-        <v>1.2451225</v>
+        <v>1.2208108</v>
       </c>
       <c r="P77">
-        <v>6.079127499999999</v>
+        <v>5.960429199999999</v>
       </c>
       <c r="Q77">
-        <v>38.2791275</v>
+        <v>38.1604292</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.190960233723175</v>
+        <v>0.1967139583645424</v>
       </c>
       <c r="T77">
-        <v>3.352430340027135</v>
+        <v>3.485310816733082</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.682866000046617</v>
+        <v>1.660723026361793</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8028,22 +8028,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1039833500074902</v>
+        <v>0.1042016415841866</v>
       </c>
       <c r="C78">
-        <v>23.11148273198168</v>
+        <v>21.38822952986146</v>
       </c>
       <c r="D78">
-        <v>137.6854827319817</v>
+        <v>137.5512295298614</v>
       </c>
       <c r="E78">
-        <v>-2.63600000000001</v>
+        <v>-1.047000000000011</v>
       </c>
       <c r="F78">
-        <v>120.764</v>
+        <v>122.353</v>
       </c>
       <c r="G78">
         <v>6.19</v>
@@ -8064,28 +8064,28 @@
         <v>18.05</v>
       </c>
       <c r="M78">
-        <v>10.86876</v>
+        <v>11.01177</v>
       </c>
       <c r="N78">
-        <v>7.181239999999999</v>
+        <v>7.038229999999999</v>
       </c>
       <c r="O78">
-        <v>1.2208108</v>
+        <v>1.1964991</v>
       </c>
       <c r="P78">
-        <v>5.960429199999999</v>
+        <v>5.841730899999999</v>
       </c>
       <c r="Q78">
-        <v>38.1604292</v>
+        <v>38.0417309</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1967139583645424</v>
+        <v>0.202968006887768</v>
       </c>
       <c r="T78">
-        <v>3.485310816733082</v>
+        <v>3.629746117500416</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.660723026361793</v>
+        <v>1.639155194850601</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8110,22 +8110,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1042016415841866</v>
+        <v>0.1044199331608831</v>
       </c>
       <c r="C79">
-        <v>21.38822952986146</v>
+        <v>19.66523788566916</v>
       </c>
       <c r="D79">
-        <v>137.5512295298614</v>
+        <v>137.4172378856692</v>
       </c>
       <c r="E79">
-        <v>-1.047000000000011</v>
+        <v>0.5420000000000016</v>
       </c>
       <c r="F79">
-        <v>122.353</v>
+        <v>123.942</v>
       </c>
       <c r="G79">
         <v>6.19</v>
@@ -8146,28 +8146,28 @@
         <v>18.05</v>
       </c>
       <c r="M79">
-        <v>11.01177</v>
+        <v>11.15478</v>
       </c>
       <c r="N79">
-        <v>7.038229999999999</v>
+        <v>6.895219999999998</v>
       </c>
       <c r="O79">
-        <v>1.1964991</v>
+        <v>1.1721874</v>
       </c>
       <c r="P79">
-        <v>5.841730899999999</v>
+        <v>5.723032599999998</v>
       </c>
       <c r="Q79">
-        <v>38.0417309</v>
+        <v>37.9230326</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.202968006887768</v>
+        <v>0.2097906052767413</v>
       </c>
       <c r="T79">
-        <v>3.629746117500416</v>
+        <v>3.787311900155689</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.639155194850601</v>
+        <v>1.618140384660208</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8192,22 +8192,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1044199331608831</v>
+        <v>0.1046382247375795</v>
       </c>
       <c r="C80">
-        <v>19.66523788566916</v>
+        <v>17.94250703578088</v>
       </c>
       <c r="D80">
-        <v>137.4172378856692</v>
+        <v>137.2835070357809</v>
       </c>
       <c r="E80">
-        <v>0.5420000000000016</v>
+        <v>2.131</v>
       </c>
       <c r="F80">
-        <v>123.942</v>
+        <v>125.531</v>
       </c>
       <c r="G80">
         <v>6.19</v>
@@ -8228,28 +8228,28 @@
         <v>18.05</v>
       </c>
       <c r="M80">
-        <v>11.15478</v>
+        <v>11.29779</v>
       </c>
       <c r="N80">
-        <v>6.895219999999998</v>
+        <v>6.752209999999998</v>
       </c>
       <c r="O80">
-        <v>1.1721874</v>
+        <v>1.1478757</v>
       </c>
       <c r="P80">
-        <v>5.723032599999998</v>
+        <v>5.604334299999998</v>
       </c>
       <c r="Q80">
-        <v>37.9230326</v>
+        <v>37.8043343</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2097906052767413</v>
+        <v>0.2172629749408549</v>
       </c>
       <c r="T80">
-        <v>3.787311900155689</v>
+        <v>3.959883947825749</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.618140384660208</v>
+        <v>1.597657594980965</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8274,22 +8274,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1046382247375795</v>
+        <v>0.104856516314276</v>
       </c>
       <c r="C81">
-        <v>17.94250703578088</v>
+        <v>16.22003621954231</v>
       </c>
       <c r="D81">
-        <v>137.2835070357809</v>
+        <v>137.1500362195423</v>
       </c>
       <c r="E81">
-        <v>2.131</v>
+        <v>3.719999999999999</v>
       </c>
       <c r="F81">
-        <v>125.531</v>
+        <v>127.12</v>
       </c>
       <c r="G81">
         <v>6.19</v>
@@ -8310,28 +8310,28 @@
         <v>18.05</v>
       </c>
       <c r="M81">
-        <v>11.29779</v>
+        <v>11.4408</v>
       </c>
       <c r="N81">
-        <v>6.752209999999998</v>
+        <v>6.609199999999998</v>
       </c>
       <c r="O81">
-        <v>1.1478757</v>
+        <v>1.123564</v>
       </c>
       <c r="P81">
-        <v>5.604334299999998</v>
+        <v>5.485635999999998</v>
       </c>
       <c r="Q81">
-        <v>37.8043343</v>
+        <v>37.685636</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2172629749408549</v>
+        <v>0.2254825815713799</v>
       </c>
       <c r="T81">
-        <v>3.959883947825749</v>
+        <v>4.149713200262815</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.597657594980965</v>
+        <v>1.577686875043703</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8356,22 +8356,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.104856516314276</v>
+        <v>0.1050748078909724</v>
       </c>
       <c r="C82">
-        <v>16.22003621954231</v>
+        <v>14.49782467925445</v>
       </c>
       <c r="D82">
-        <v>137.1500362195423</v>
+        <v>137.0168246792545</v>
       </c>
       <c r="E82">
-        <v>3.719999999999999</v>
+        <v>5.309000000000012</v>
       </c>
       <c r="F82">
-        <v>127.12</v>
+        <v>128.709</v>
       </c>
       <c r="G82">
         <v>6.19</v>
@@ -8392,28 +8392,28 @@
         <v>18.05</v>
       </c>
       <c r="M82">
-        <v>11.4408</v>
+        <v>11.58381</v>
       </c>
       <c r="N82">
-        <v>6.609199999999998</v>
+        <v>6.466189999999997</v>
       </c>
       <c r="O82">
-        <v>1.123564</v>
+        <v>1.0992523</v>
       </c>
       <c r="P82">
-        <v>5.485635999999998</v>
+        <v>5.366937699999998</v>
       </c>
       <c r="Q82">
-        <v>37.685636</v>
+        <v>37.5669377</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2254825815713799</v>
+        <v>0.2345674099524865</v>
       </c>
       <c r="T82">
-        <v>4.149713200262815</v>
+        <v>4.359524479272206</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.577686875043703</v>
+        <v>1.558209259302423</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8438,22 +8438,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1050748078909724</v>
+        <v>0.1052930994676689</v>
       </c>
       <c r="C83">
-        <v>14.49782467925445</v>
+        <v>12.77587166015917</v>
       </c>
       <c r="D83">
-        <v>137.0168246792545</v>
+        <v>136.8838716601592</v>
       </c>
       <c r="E83">
-        <v>5.309000000000012</v>
+        <v>6.89800000000001</v>
       </c>
       <c r="F83">
-        <v>128.709</v>
+        <v>130.298</v>
       </c>
       <c r="G83">
         <v>6.19</v>
@@ -8474,28 +8474,28 @@
         <v>18.05</v>
       </c>
       <c r="M83">
-        <v>11.58381</v>
+        <v>11.72682</v>
       </c>
       <c r="N83">
-        <v>6.466189999999997</v>
+        <v>6.323179999999997</v>
       </c>
       <c r="O83">
-        <v>1.0992523</v>
+        <v>1.0749406</v>
       </c>
       <c r="P83">
-        <v>5.366937699999998</v>
+        <v>5.248239399999997</v>
       </c>
       <c r="Q83">
-        <v>37.5669377</v>
+        <v>37.4482394</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2345674099524865</v>
+        <v>0.2446616637092716</v>
       </c>
       <c r="T83">
-        <v>4.359524479272206</v>
+        <v>4.592648122615972</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.558209259302423</v>
+        <v>1.53920670735971</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8520,22 +8520,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1052930994676689</v>
+        <v>0.1055113910443653</v>
       </c>
       <c r="C84">
-        <v>12.77587166015917</v>
+        <v>11.05417641042499</v>
       </c>
       <c r="D84">
-        <v>136.8838716601592</v>
+        <v>136.751176410425</v>
       </c>
       <c r="E84">
-        <v>6.89800000000001</v>
+        <v>8.487000000000009</v>
       </c>
       <c r="F84">
-        <v>130.298</v>
+        <v>131.887</v>
       </c>
       <c r="G84">
         <v>6.19</v>
@@ -8556,28 +8556,28 @@
         <v>18.05</v>
       </c>
       <c r="M84">
-        <v>11.72682</v>
+        <v>11.86983</v>
       </c>
       <c r="N84">
-        <v>6.323179999999997</v>
+        <v>6.180169999999997</v>
       </c>
       <c r="O84">
-        <v>1.0749406</v>
+        <v>1.0506289</v>
       </c>
       <c r="P84">
-        <v>5.248239399999997</v>
+        <v>5.129541099999997</v>
       </c>
       <c r="Q84">
-        <v>37.4482394</v>
+        <v>37.3295411</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2446616637092716</v>
+        <v>0.2559434767315608</v>
       </c>
       <c r="T84">
-        <v>4.592648122615972</v>
+        <v>4.853198076941357</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.53920670735971</v>
+        <v>1.520662048234894</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8602,22 +8602,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1055113910443653</v>
+        <v>0.1057296826210618</v>
       </c>
       <c r="C85">
-        <v>11.05417641042499</v>
+        <v>9.332738181132896</v>
       </c>
       <c r="D85">
-        <v>136.751176410425</v>
+        <v>136.6187381811329</v>
       </c>
       <c r="E85">
-        <v>8.487000000000009</v>
+        <v>10.07600000000001</v>
       </c>
       <c r="F85">
-        <v>131.887</v>
+        <v>133.476</v>
       </c>
       <c r="G85">
         <v>6.19</v>
@@ -8638,28 +8638,28 @@
         <v>18.05</v>
       </c>
       <c r="M85">
-        <v>11.86983</v>
+        <v>12.01284</v>
       </c>
       <c r="N85">
-        <v>6.180169999999997</v>
+        <v>6.037159999999998</v>
       </c>
       <c r="O85">
-        <v>1.0506289</v>
+        <v>1.0263172</v>
       </c>
       <c r="P85">
-        <v>5.129541099999997</v>
+        <v>5.010842799999999</v>
       </c>
       <c r="Q85">
-        <v>37.3295411</v>
+        <v>37.2108428</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2559434767315608</v>
+        <v>0.2686355163816362</v>
       </c>
       <c r="T85">
-        <v>4.853198076941357</v>
+        <v>5.146316775557418</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.520662048234894</v>
+        <v>1.502558928613051</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8684,22 +8684,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1057296826210617</v>
+        <v>0.1484609035767477</v>
       </c>
       <c r="C86">
-        <v>9.332738181132953</v>
+        <v>-14.02872363404077</v>
       </c>
       <c r="D86">
-        <v>136.6187381811329</v>
+        <v>114.8462763659592</v>
       </c>
       <c r="E86">
-        <v>10.07599999999998</v>
+        <v>11.66499999999998</v>
       </c>
       <c r="F86">
-        <v>133.476</v>
+        <v>135.065</v>
       </c>
       <c r="G86">
         <v>6.19</v>
@@ -8720,45 +8720,45 @@
         <v>18.05</v>
       </c>
       <c r="M86">
-        <v>12.01284</v>
+        <v>19.827542</v>
       </c>
       <c r="N86">
-        <v>6.03716</v>
+        <v>-1.777542</v>
       </c>
       <c r="O86">
-        <v>1.0263172</v>
+        <v>-0.3021821400000001</v>
       </c>
       <c r="P86">
-        <v>5.0108428</v>
+        <v>-1.47535986</v>
       </c>
       <c r="Q86">
-        <v>37.2108428</v>
+        <v>30.72464014</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.268635516381636</v>
+        <v>0.2866119395152171</v>
       </c>
       <c r="T86">
-        <v>5.146316775557414</v>
+        <v>5.561476663168985</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.17</v>
+        <v>0.1547594754811262</v>
       </c>
       <c r="W86">
-        <v>0.07469999999999999</v>
+        <v>0.1240813089993707</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.502558928613051</v>
+        <v>0.9103498557713305</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8766,22 +8766,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1484609035767477</v>
+        <v>0.1494709035767476</v>
       </c>
       <c r="C87">
-        <v>-14.02872363404077</v>
+        <v>-16.04870394297809</v>
       </c>
       <c r="D87">
-        <v>114.8462763659592</v>
+        <v>114.4152960570219</v>
       </c>
       <c r="E87">
-        <v>11.66499999999998</v>
+        <v>13.25399999999998</v>
       </c>
       <c r="F87">
-        <v>135.065</v>
+        <v>136.654</v>
       </c>
       <c r="G87">
         <v>6.19</v>
@@ -8802,37 +8802,37 @@
         <v>18.05</v>
       </c>
       <c r="M87">
-        <v>19.827542</v>
+        <v>20.0608072</v>
       </c>
       <c r="N87">
-        <v>-1.777542</v>
+        <v>-2.010807199999999</v>
       </c>
       <c r="O87">
-        <v>-0.3021821400000001</v>
+        <v>-0.3418372239999998</v>
       </c>
       <c r="P87">
-        <v>-1.47535986</v>
+        <v>-1.668969975999999</v>
       </c>
       <c r="Q87">
-        <v>30.72464014</v>
+        <v>30.531030024</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2866119395152171</v>
+        <v>0.3038127923377326</v>
       </c>
       <c r="T87">
-        <v>5.561476663168985</v>
+        <v>5.958724996252485</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1547594754811262</v>
+        <v>0.152959946696462</v>
       </c>
       <c r="W87">
-        <v>0.1240813089993707</v>
+        <v>0.1243454798249594</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9103498557713305</v>
+        <v>0.8997643923321291</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8848,22 +8848,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1494709035767476</v>
+        <v>0.1504809035767476</v>
       </c>
       <c r="C88">
-        <v>-16.04870394297809</v>
+        <v>-18.065461690379</v>
       </c>
       <c r="D88">
-        <v>114.4152960570219</v>
+        <v>113.987538309621</v>
       </c>
       <c r="E88">
-        <v>13.25399999999998</v>
+        <v>14.84299999999998</v>
       </c>
       <c r="F88">
-        <v>136.654</v>
+        <v>138.243</v>
       </c>
       <c r="G88">
         <v>6.19</v>
@@ -8884,37 +8884,37 @@
         <v>18.05</v>
       </c>
       <c r="M88">
-        <v>20.0608072</v>
+        <v>20.2940724</v>
       </c>
       <c r="N88">
-        <v>-2.010807199999999</v>
+        <v>-2.2440724</v>
       </c>
       <c r="O88">
-        <v>-0.3418372239999998</v>
+        <v>-0.3814923080000001</v>
       </c>
       <c r="P88">
-        <v>-1.668969975999999</v>
+        <v>-1.862580092</v>
       </c>
       <c r="Q88">
-        <v>30.531030024</v>
+        <v>30.337419908</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3038127923377326</v>
+        <v>0.3236599302098659</v>
       </c>
       <c r="T88">
-        <v>5.958724996252485</v>
+        <v>6.417088457502677</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.152959946696462</v>
+        <v>0.1512017863896061</v>
       </c>
       <c r="W88">
-        <v>0.1243454798249594</v>
+        <v>0.1246035777580058</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8997643923321291</v>
+        <v>0.8894222728800356</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8930,22 +8930,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1504809035767476</v>
+        <v>0.1514909035767477</v>
       </c>
       <c r="C89">
-        <v>-18.065461690379</v>
+        <v>-20.07903288562203</v>
       </c>
       <c r="D89">
-        <v>113.987538309621</v>
+        <v>113.562967114378</v>
       </c>
       <c r="E89">
-        <v>14.84299999999998</v>
+        <v>16.432</v>
       </c>
       <c r="F89">
-        <v>138.243</v>
+        <v>139.832</v>
       </c>
       <c r="G89">
         <v>6.19</v>
@@ -8966,37 +8966,37 @@
         <v>18.05</v>
       </c>
       <c r="M89">
-        <v>20.2940724</v>
+        <v>20.5273376</v>
       </c>
       <c r="N89">
-        <v>-2.2440724</v>
+        <v>-2.477337600000006</v>
       </c>
       <c r="O89">
-        <v>-0.3814923080000001</v>
+        <v>-0.421147392000001</v>
       </c>
       <c r="P89">
-        <v>-1.862580092</v>
+        <v>-2.056190208000005</v>
       </c>
       <c r="Q89">
-        <v>30.337419908</v>
+        <v>30.143809792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3236599302098659</v>
+        <v>0.3468149243940215</v>
       </c>
       <c r="T89">
-        <v>6.417088457502677</v>
+        <v>6.951845828961234</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1512017863896061</v>
+        <v>0.1494835842715423</v>
       </c>
       <c r="W89">
-        <v>0.1246035777580058</v>
+        <v>0.1248558098289376</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8894222728800356</v>
+        <v>0.8793152015973077</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9012,22 +9012,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1514909035767477</v>
+        <v>0.1525009035767476</v>
       </c>
       <c r="C90">
-        <v>-20.07903288562203</v>
+        <v>-22.08945300357765</v>
       </c>
       <c r="D90">
-        <v>113.562967114378</v>
+        <v>113.1415469964223</v>
       </c>
       <c r="E90">
-        <v>16.432</v>
+        <v>18.021</v>
       </c>
       <c r="F90">
-        <v>139.832</v>
+        <v>141.421</v>
       </c>
       <c r="G90">
         <v>6.19</v>
@@ -9048,37 +9048,37 @@
         <v>18.05</v>
       </c>
       <c r="M90">
-        <v>20.5273376</v>
+        <v>20.7606028</v>
       </c>
       <c r="N90">
-        <v>-2.477337600000006</v>
+        <v>-2.710602800000004</v>
       </c>
       <c r="O90">
-        <v>-0.421147392000001</v>
+        <v>-0.4608024760000007</v>
       </c>
       <c r="P90">
-        <v>-2.056190208000005</v>
+        <v>-2.249800324000003</v>
       </c>
       <c r="Q90">
-        <v>30.143809792</v>
+        <v>29.950199676</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3468149243940215</v>
+        <v>0.3741799175207506</v>
       </c>
       <c r="T90">
-        <v>6.951845828961234</v>
+        <v>7.583831813412255</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1494835842715423</v>
+        <v>0.1478039934370306</v>
       </c>
       <c r="W90">
-        <v>0.1248558098289376</v>
+        <v>0.1251023737634439</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8793152015973077</v>
+        <v>0.8694352555119448</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9094,22 +9094,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1525009035767476</v>
+        <v>0.1535109035767477</v>
       </c>
       <c r="C91">
-        <v>-22.08945300357765</v>
+        <v>-24.0967569944894</v>
       </c>
       <c r="D91">
-        <v>113.1415469964223</v>
+        <v>112.7232430055106</v>
       </c>
       <c r="E91">
-        <v>18.021</v>
+        <v>19.61</v>
       </c>
       <c r="F91">
-        <v>141.421</v>
+        <v>143.01</v>
       </c>
       <c r="G91">
         <v>6.19</v>
@@ -9130,37 +9130,37 @@
         <v>18.05</v>
       </c>
       <c r="M91">
-        <v>20.7606028</v>
+        <v>20.993868</v>
       </c>
       <c r="N91">
-        <v>-2.710602800000004</v>
+        <v>-2.943868000000002</v>
       </c>
       <c r="O91">
-        <v>-0.4608024760000007</v>
+        <v>-0.5004575600000004</v>
       </c>
       <c r="P91">
-        <v>-2.249800324000003</v>
+        <v>-2.443410440000001</v>
       </c>
       <c r="Q91">
-        <v>29.950199676</v>
+        <v>29.75658956</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3741799175207506</v>
+        <v>0.4070179092728258</v>
       </c>
       <c r="T91">
-        <v>7.583831813412255</v>
+        <v>8.342214994753482</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1478039934370306</v>
+        <v>0.1461617268432858</v>
       </c>
       <c r="W91">
-        <v>0.1251023737634439</v>
+        <v>0.1253434584994056</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8694352555119448</v>
+        <v>0.8597748637840343</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9176,22 +9176,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1535109035767477</v>
+        <v>0.1545209035767477</v>
       </c>
       <c r="C92">
-        <v>-24.0967569944894</v>
+        <v>-26.10097929363613</v>
       </c>
       <c r="D92">
-        <v>112.7232430055106</v>
+        <v>112.3080207063639</v>
       </c>
       <c r="E92">
-        <v>19.61</v>
+        <v>21.199</v>
       </c>
       <c r="F92">
-        <v>143.01</v>
+        <v>144.599</v>
       </c>
       <c r="G92">
         <v>6.19</v>
@@ -9212,37 +9212,37 @@
         <v>18.05</v>
       </c>
       <c r="M92">
-        <v>20.993868</v>
+        <v>21.2271332</v>
       </c>
       <c r="N92">
-        <v>-2.943868000000002</v>
+        <v>-3.177133200000004</v>
       </c>
       <c r="O92">
-        <v>-0.5004575600000004</v>
+        <v>-0.5401126440000007</v>
       </c>
       <c r="P92">
-        <v>-2.443410440000001</v>
+        <v>-2.637020556000003</v>
       </c>
       <c r="Q92">
-        <v>29.75658956</v>
+        <v>29.562979444</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4070179092728258</v>
+        <v>0.447153232525362</v>
       </c>
       <c r="T92">
-        <v>8.342214994753482</v>
+        <v>9.269127771948314</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1461617268432858</v>
+        <v>0.1445555540208321</v>
       </c>
       <c r="W92">
-        <v>0.1253434584994056</v>
+        <v>0.1255792446697419</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8597748637840343</v>
+        <v>0.8503267883578361</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9258,22 +9258,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1545209035767477</v>
+        <v>0.1555309035767477</v>
       </c>
       <c r="C93">
-        <v>-26.10097929363613</v>
+        <v>-28.10215383078175</v>
       </c>
       <c r="D93">
-        <v>112.3080207063639</v>
+        <v>111.8958461692182</v>
       </c>
       <c r="E93">
-        <v>21.199</v>
+        <v>22.788</v>
       </c>
       <c r="F93">
-        <v>144.599</v>
+        <v>146.188</v>
       </c>
       <c r="G93">
         <v>6.19</v>
@@ -9294,37 +9294,37 @@
         <v>18.05</v>
       </c>
       <c r="M93">
-        <v>21.2271332</v>
+        <v>21.4603984</v>
       </c>
       <c r="N93">
-        <v>-3.177133200000004</v>
+        <v>-3.410398400000002</v>
       </c>
       <c r="O93">
-        <v>-0.5401126440000007</v>
+        <v>-0.5797677280000003</v>
       </c>
       <c r="P93">
-        <v>-2.637020556000003</v>
+        <v>-2.830630672000002</v>
       </c>
       <c r="Q93">
-        <v>29.562979444</v>
+        <v>29.369369328</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.447153232525362</v>
+        <v>0.4973223865910323</v>
       </c>
       <c r="T93">
-        <v>9.269127771948314</v>
+        <v>10.42776874344186</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1445555540208321</v>
+        <v>0.1429842979988666</v>
       </c>
       <c r="W93">
-        <v>0.1255792446697419</v>
+        <v>0.1258099050537664</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8503267883578361</v>
+        <v>0.8410841058756858</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9340,22 +9340,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1555309035767477</v>
+        <v>0.1565409035767476</v>
       </c>
       <c r="C94">
-        <v>-28.10215383078175</v>
+        <v>-30.10031403941765</v>
       </c>
       <c r="D94">
-        <v>111.8958461692182</v>
+        <v>111.4866859605823</v>
       </c>
       <c r="E94">
-        <v>22.788</v>
+        <v>24.377</v>
       </c>
       <c r="F94">
-        <v>146.188</v>
+        <v>147.777</v>
       </c>
       <c r="G94">
         <v>6.19</v>
@@ -9376,37 +9376,37 @@
         <v>18.05</v>
       </c>
       <c r="M94">
-        <v>21.4603984</v>
+        <v>21.6936636</v>
       </c>
       <c r="N94">
-        <v>-3.410398400000002</v>
+        <v>-3.643663600000004</v>
       </c>
       <c r="O94">
-        <v>-0.5797677280000003</v>
+        <v>-0.6194228120000006</v>
       </c>
       <c r="P94">
-        <v>-2.830630672000002</v>
+        <v>-3.024240788000003</v>
       </c>
       <c r="Q94">
-        <v>29.369369328</v>
+        <v>29.175759212</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4973223865910323</v>
+        <v>0.5618255846754654</v>
       </c>
       <c r="T94">
-        <v>10.42776874344186</v>
+        <v>11.91744999250498</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1429842979988666</v>
+        <v>0.1414468324289863</v>
       </c>
       <c r="W94">
-        <v>0.1258099050537664</v>
+        <v>0.1260356049994248</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8410841058756858</v>
+        <v>0.8320401907587429</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9422,22 +9422,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1565409035767476</v>
+        <v>0.1575509035767476</v>
       </c>
       <c r="C95">
-        <v>-30.10031403941765</v>
+        <v>-32.09549286580304</v>
       </c>
       <c r="D95">
-        <v>111.4866859605823</v>
+        <v>111.0805071341969</v>
       </c>
       <c r="E95">
-        <v>24.377</v>
+        <v>25.96599999999999</v>
       </c>
       <c r="F95">
-        <v>147.777</v>
+        <v>149.366</v>
       </c>
       <c r="G95">
         <v>6.19</v>
@@ -9458,37 +9458,37 @@
         <v>18.05</v>
       </c>
       <c r="M95">
-        <v>21.6936636</v>
+        <v>21.9269288</v>
       </c>
       <c r="N95">
-        <v>-3.643663600000004</v>
+        <v>-3.876928800000002</v>
       </c>
       <c r="O95">
-        <v>-0.6194228120000006</v>
+        <v>-0.6590778960000003</v>
       </c>
       <c r="P95">
-        <v>-3.024240788000003</v>
+        <v>-3.217850904000001</v>
       </c>
       <c r="Q95">
-        <v>29.175759212</v>
+        <v>28.982149096</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5618255846754654</v>
+        <v>0.6478298487880433</v>
       </c>
       <c r="T95">
-        <v>11.91744999250498</v>
+        <v>13.90369165792248</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1414468324289863</v>
+        <v>0.1399420788925077</v>
       </c>
       <c r="W95">
-        <v>0.1260356049994248</v>
+        <v>0.1262565028185799</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8320401907587429</v>
+        <v>0.8231886993676925</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9504,22 +9504,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1575509035767476</v>
+        <v>0.1585609035767477</v>
       </c>
       <c r="C96">
-        <v>-32.09549286580304</v>
+        <v>-34.08772277780824</v>
       </c>
       <c r="D96">
-        <v>111.0805071341969</v>
+        <v>110.6772772221917</v>
       </c>
       <c r="E96">
-        <v>25.96599999999999</v>
+        <v>27.55499999999999</v>
       </c>
       <c r="F96">
-        <v>149.366</v>
+        <v>150.955</v>
       </c>
       <c r="G96">
         <v>6.19</v>
@@ -9540,37 +9540,37 @@
         <v>18.05</v>
       </c>
       <c r="M96">
-        <v>21.9269288</v>
+        <v>22.160194</v>
       </c>
       <c r="N96">
-        <v>-3.876928800000002</v>
+        <v>-4.110194000000003</v>
       </c>
       <c r="O96">
-        <v>-0.6590778960000003</v>
+        <v>-0.6987329800000006</v>
       </c>
       <c r="P96">
-        <v>-3.217850904000001</v>
+        <v>-3.411461020000003</v>
       </c>
       <c r="Q96">
-        <v>28.982149096</v>
+        <v>28.78853898</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6478298487880433</v>
+        <v>0.7682358185456521</v>
       </c>
       <c r="T96">
-        <v>13.90369165792248</v>
+        <v>16.68442998950698</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1399420788925077</v>
+        <v>0.1384690043778498</v>
       </c>
       <c r="W96">
-        <v>0.1262565028185799</v>
+        <v>0.1264727501573317</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8231886993676925</v>
+        <v>0.8145235551638219</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9586,22 +9586,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1585609035767477</v>
+        <v>0.1595709035767477</v>
       </c>
       <c r="C97">
-        <v>-34.08772277780824</v>
+        <v>-36.07703577356642</v>
       </c>
       <c r="D97">
-        <v>110.6772772221917</v>
+        <v>110.2769642264336</v>
       </c>
       <c r="E97">
-        <v>27.55499999999999</v>
+        <v>29.14399999999999</v>
       </c>
       <c r="F97">
-        <v>150.955</v>
+        <v>152.544</v>
       </c>
       <c r="G97">
         <v>6.19</v>
@@ -9622,37 +9622,37 @@
         <v>18.05</v>
       </c>
       <c r="M97">
-        <v>22.160194</v>
+        <v>22.3934592</v>
       </c>
       <c r="N97">
-        <v>-4.110194000000003</v>
+        <v>-4.343459200000002</v>
       </c>
       <c r="O97">
-        <v>-0.6987329800000006</v>
+        <v>-0.7383880640000003</v>
       </c>
       <c r="P97">
-        <v>-3.411461020000003</v>
+        <v>-3.605071136000001</v>
       </c>
       <c r="Q97">
-        <v>28.78853898</v>
+        <v>28.594928864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7682358185456521</v>
+        <v>0.9488447731820658</v>
       </c>
       <c r="T97">
-        <v>16.68442998950698</v>
+        <v>20.85553748688374</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1384690043778498</v>
+        <v>0.1370266189155805</v>
       </c>
       <c r="W97">
-        <v>0.1264727501573317</v>
+        <v>0.1266844923431928</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8145235551638219</v>
+        <v>0.8060389347975322</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9668,22 +9668,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1595709035767477</v>
+        <v>0.2144322958056769</v>
       </c>
       <c r="C98">
-        <v>-36.07703577356642</v>
+        <v>-55.77406695508049</v>
       </c>
       <c r="D98">
-        <v>110.2769642264336</v>
+        <v>92.1689330449195</v>
       </c>
       <c r="E98">
-        <v>29.14399999999999</v>
+        <v>30.73299999999999</v>
       </c>
       <c r="F98">
-        <v>152.544</v>
+        <v>154.133</v>
       </c>
       <c r="G98">
         <v>6.19</v>
@@ -9704,45 +9704,45 @@
         <v>18.05</v>
       </c>
       <c r="M98">
-        <v>22.3934592</v>
+        <v>30.9499064</v>
       </c>
       <c r="N98">
-        <v>-4.343459200000002</v>
+        <v>-12.8999064</v>
       </c>
       <c r="O98">
-        <v>-0.7383880640000003</v>
+        <v>-2.192984088</v>
       </c>
       <c r="P98">
-        <v>-3.605071136000001</v>
+        <v>-10.706922312</v>
       </c>
       <c r="Q98">
-        <v>28.594928864</v>
+        <v>21.493077688</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9488447731820634</v>
+        <v>1.298906105207059</v>
       </c>
       <c r="T98">
-        <v>20.85553748688368</v>
+        <v>28.94009480847711</v>
       </c>
       <c r="U98">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1370266189155805</v>
+        <v>0.09914408012555412</v>
       </c>
       <c r="W98">
-        <v>0.1266844923431928</v>
+        <v>0.1808918687107887</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8060389347975322</v>
+        <v>0.5832004713267889</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9750,22 +9750,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2144322958056769</v>
+        <v>0.2159822958056769</v>
       </c>
       <c r="C99">
-        <v>-55.77406695508049</v>
+        <v>-57.78869056168601</v>
       </c>
       <c r="D99">
-        <v>92.1689330449195</v>
+        <v>91.74330943831397</v>
       </c>
       <c r="E99">
-        <v>30.73299999999999</v>
+        <v>32.32199999999999</v>
       </c>
       <c r="F99">
-        <v>154.133</v>
+        <v>155.722</v>
       </c>
       <c r="G99">
         <v>6.19</v>
@@ -9786,37 +9786,37 @@
         <v>18.05</v>
       </c>
       <c r="M99">
-        <v>30.9499064</v>
+        <v>31.2689776</v>
       </c>
       <c r="N99">
-        <v>-12.8999064</v>
+        <v>-13.2189776</v>
       </c>
       <c r="O99">
-        <v>-2.192984088</v>
+        <v>-2.247226192</v>
       </c>
       <c r="P99">
-        <v>-10.706922312</v>
+        <v>-10.971751408</v>
       </c>
       <c r="Q99">
-        <v>21.493077688</v>
+        <v>21.228248592</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.298906105207059</v>
+        <v>1.925459157810588</v>
       </c>
       <c r="T99">
-        <v>28.94009480847711</v>
+        <v>43.41014221271567</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09914408012555412</v>
+        <v>0.09813240583855867</v>
       </c>
       <c r="W99">
-        <v>0.1808918687107887</v>
+        <v>0.1810950129076174</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5832004713267889</v>
+        <v>0.5772494461091686</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9832,22 +9832,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2159822958056769</v>
+        <v>0.2175322958056769</v>
       </c>
       <c r="C100">
-        <v>-57.78869056168601</v>
+        <v>-59.79940129347361</v>
       </c>
       <c r="D100">
-        <v>91.74330943831397</v>
+        <v>91.32159870652637</v>
       </c>
       <c r="E100">
-        <v>32.32199999999999</v>
+        <v>33.91099999999999</v>
       </c>
       <c r="F100">
-        <v>155.722</v>
+        <v>157.311</v>
       </c>
       <c r="G100">
         <v>6.19</v>
@@ -9868,37 +9868,37 @@
         <v>18.05</v>
       </c>
       <c r="M100">
-        <v>31.2689776</v>
+        <v>31.5880488</v>
       </c>
       <c r="N100">
-        <v>-13.2189776</v>
+        <v>-13.5380488</v>
       </c>
       <c r="O100">
-        <v>-2.247226192</v>
+        <v>-2.301468296</v>
       </c>
       <c r="P100">
-        <v>-10.971751408</v>
+        <v>-11.236580504</v>
       </c>
       <c r="Q100">
-        <v>21.228248592</v>
+        <v>20.963419496</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.925459157810588</v>
+        <v>3.805118315621176</v>
       </c>
       <c r="T100">
-        <v>43.41014221271567</v>
+        <v>86.82028442543132</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09813240583855867</v>
+        <v>0.09714116941594696</v>
       </c>
       <c r="W100">
-        <v>0.1810950129076174</v>
+        <v>0.1812940531812779</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9906,91 +9906,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5772494461091686</v>
+        <v>0.5714186436232174</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2175322958056769</v>
-      </c>
-      <c r="C101">
-        <v>-59.79940129347361</v>
-      </c>
-      <c r="D101">
-        <v>91.32159870652637</v>
-      </c>
-      <c r="E101">
-        <v>33.91099999999999</v>
-      </c>
-      <c r="F101">
-        <v>157.311</v>
-      </c>
-      <c r="G101">
-        <v>6.19</v>
-      </c>
-      <c r="H101">
-        <v>35.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>50.25</v>
-      </c>
-      <c r="K101">
-        <v>32.2</v>
-      </c>
-      <c r="L101">
-        <v>18.05</v>
-      </c>
-      <c r="M101">
-        <v>31.5880488</v>
-      </c>
-      <c r="N101">
-        <v>-13.5380488</v>
-      </c>
-      <c r="O101">
-        <v>-2.301468296</v>
-      </c>
-      <c r="P101">
-        <v>-11.236580504</v>
-      </c>
-      <c r="Q101">
-        <v>20.963419496</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.805118315621176</v>
-      </c>
-      <c r="T101">
-        <v>86.82028442543132</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09714116941594696</v>
-      </c>
-      <c r="W101">
-        <v>0.1812940531812779</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5714186436232174</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
